--- a/howell7.xlsx
+++ b/howell7.xlsx
@@ -506,7 +506,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>For public domain. No rights reserved. Generated on Feb 19, 2026.</t>
+          <t>For public domain. No rights reserved. Generated on Mar 07, 2026.</t>
         </is>
       </c>
     </row>
@@ -590,12 +590,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 64</t>
+          <t>Name 61</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name 47</t>
+          <t>Name 78</t>
         </is>
       </c>
       <c r="D10" s="4">
@@ -613,12 +613,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Name 43</t>
+          <t>Name 58</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Name 36</t>
+          <t>Name 59</t>
         </is>
       </c>
       <c r="D11" s="4">
@@ -636,12 +636,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Name 42</t>
+          <t>Name 48</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Name 82</t>
+          <t>Name 23</t>
         </is>
       </c>
       <c r="D12" s="4">
@@ -659,12 +659,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Name 90</t>
+          <t>Name 76</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Name 66</t>
+          <t>Name 20</t>
         </is>
       </c>
       <c r="D13" s="4">
@@ -682,12 +682,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Name 43</t>
+          <t>Name 60</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Name 67</t>
+          <t>Name 37</t>
         </is>
       </c>
       <c r="D14" s="4">
@@ -705,12 +705,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Name 72</t>
+          <t>Name 26</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Name 24</t>
+          <t>Name 43</t>
         </is>
       </c>
       <c r="D15" s="4">
@@ -728,12 +728,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Name 30</t>
+          <t>Name 80</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Name 39</t>
+          <t>Name 71</t>
         </is>
       </c>
       <c r="D16" s="4">

--- a/howell7.xlsx
+++ b/howell7.xlsx
@@ -590,12 +590,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 61</t>
+          <t>Name 66</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name 78</t>
+          <t>Name 84</t>
         </is>
       </c>
       <c r="D10" s="4">
@@ -613,12 +613,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Name 58</t>
+          <t>Name 16</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Name 59</t>
+          <t>Name 28</t>
         </is>
       </c>
       <c r="D11" s="4">
@@ -636,12 +636,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Name 48</t>
+          <t>Name 86</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Name 23</t>
+          <t>Name 59</t>
         </is>
       </c>
       <c r="D12" s="4">
@@ -659,12 +659,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Name 76</t>
+          <t>Name 83</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Name 20</t>
+          <t>Name 26</t>
         </is>
       </c>
       <c r="D13" s="4">
@@ -682,12 +682,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Name 60</t>
+          <t>Name 88</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Name 37</t>
+          <t>Name 48</t>
         </is>
       </c>
       <c r="D14" s="4">
@@ -705,12 +705,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Name 26</t>
+          <t>Name 60</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Name 43</t>
+          <t>Name 28</t>
         </is>
       </c>
       <c r="D15" s="4">
@@ -728,12 +728,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Name 80</t>
+          <t>Name 66</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Name 71</t>
+          <t>Name 17</t>
         </is>
       </c>
       <c r="D16" s="4">

--- a/howell7.xlsx
+++ b/howell7.xlsx
@@ -506,7 +506,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>For public domain. No rights reserved. Generated on Mar 07, 2026.</t>
+          <t>For public domain. No rights reserved. Generated on Mar 08, 2026.</t>
         </is>
       </c>
     </row>
@@ -590,12 +590,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 66</t>
+          <t>Name 55</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name 84</t>
+          <t>Name 16</t>
         </is>
       </c>
       <c r="D10" s="4">
@@ -613,12 +613,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Name 16</t>
+          <t>Name 31</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Name 28</t>
+          <t>Name 47</t>
         </is>
       </c>
       <c r="D11" s="4">
@@ -636,12 +636,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Name 86</t>
+          <t>Name 67</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Name 59</t>
+          <t>Name 73</t>
         </is>
       </c>
       <c r="D12" s="4">
@@ -659,12 +659,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Name 83</t>
+          <t>Name 57</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Name 26</t>
+          <t>Name 76</t>
         </is>
       </c>
       <c r="D13" s="4">
@@ -682,12 +682,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Name 88</t>
+          <t>Name 29</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Name 48</t>
+          <t>Name 64</t>
         </is>
       </c>
       <c r="D14" s="4">
@@ -705,12 +705,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Name 60</t>
+          <t>Name 72</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Name 28</t>
+          <t>Name 63</t>
         </is>
       </c>
       <c r="D15" s="4">
@@ -728,12 +728,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Name 66</t>
+          <t>Name 79</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Name 17</t>
+          <t>Name 67</t>
         </is>
       </c>
       <c r="D16" s="4">

--- a/howell7.xlsx
+++ b/howell7.xlsx
@@ -590,12 +590,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 55</t>
+          <t>Name 83</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name 16</t>
+          <t>Name 47</t>
         </is>
       </c>
       <c r="D10" s="4">
@@ -613,12 +613,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Name 31</t>
+          <t>Name 35</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Name 47</t>
+          <t>Name 74</t>
         </is>
       </c>
       <c r="D11" s="4">
@@ -636,12 +636,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Name 67</t>
+          <t>Name 78</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Name 73</t>
+          <t>Name 72</t>
         </is>
       </c>
       <c r="D12" s="4">
@@ -659,12 +659,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Name 57</t>
+          <t>Name 83</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Name 76</t>
+          <t>Name 88</t>
         </is>
       </c>
       <c r="D13" s="4">
@@ -682,12 +682,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Name 29</t>
+          <t>Name 79</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Name 64</t>
+          <t>Name 15</t>
         </is>
       </c>
       <c r="D14" s="4">
@@ -705,12 +705,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Name 72</t>
+          <t>Name 85</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Name 63</t>
+          <t>Name 67</t>
         </is>
       </c>
       <c r="D15" s="4">
@@ -728,12 +728,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Name 79</t>
+          <t>Name 28</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Name 67</t>
+          <t>Name 33</t>
         </is>
       </c>
       <c r="D16" s="4">

--- a/howell7.xlsx
+++ b/howell7.xlsx
@@ -506,7 +506,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>For public domain. No rights reserved. Generated on Mar 08, 2026.</t>
+          <t>For public domain. No rights reserved. Generated on Mar 10, 2026.</t>
         </is>
       </c>
     </row>
@@ -590,12 +590,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 83</t>
+          <t>Name 66</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name 47</t>
+          <t>Name 78</t>
         </is>
       </c>
       <c r="D10" s="4">
@@ -613,12 +613,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Name 35</t>
+          <t>Name 66</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Name 74</t>
+          <t>Name 11</t>
         </is>
       </c>
       <c r="D11" s="4">
@@ -636,12 +636,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Name 78</t>
+          <t>Name 27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Name 72</t>
+          <t>Name 25</t>
         </is>
       </c>
       <c r="D12" s="4">
@@ -659,12 +659,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Name 83</t>
+          <t>Name 28</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Name 88</t>
+          <t>Name 84</t>
         </is>
       </c>
       <c r="D13" s="4">
@@ -682,12 +682,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Name 79</t>
+          <t>Name 54</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Name 15</t>
+          <t>Name 54</t>
         </is>
       </c>
       <c r="D14" s="4">
@@ -705,12 +705,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Name 85</t>
+          <t>Name 73</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Name 67</t>
+          <t>Name 61</t>
         </is>
       </c>
       <c r="D15" s="4">
@@ -728,12 +728,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Name 28</t>
+          <t>Name 83</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Name 33</t>
+          <t>Name 49</t>
         </is>
       </c>
       <c r="D16" s="4">

--- a/howell7.xlsx
+++ b/howell7.xlsx
@@ -506,7 +506,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>For public domain. No rights reserved. Generated on Mar 10, 2026.</t>
+          <t>For public domain. No rights reserved. Generated on Mar 11, 2026.</t>
         </is>
       </c>
     </row>
@@ -590,12 +590,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 66</t>
+          <t>Name 24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name 78</t>
+          <t>Name 21</t>
         </is>
       </c>
       <c r="D10" s="4">
@@ -613,12 +613,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Name 66</t>
+          <t>Name 59</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Name 11</t>
+          <t>Name 60</t>
         </is>
       </c>
       <c r="D11" s="4">
@@ -636,12 +636,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Name 27</t>
+          <t>Name 41</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Name 25</t>
+          <t>Name 55</t>
         </is>
       </c>
       <c r="D12" s="4">
@@ -659,12 +659,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Name 28</t>
+          <t>Name 15</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Name 84</t>
+          <t>Name 76</t>
         </is>
       </c>
       <c r="D13" s="4">
@@ -682,12 +682,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Name 54</t>
+          <t>Name 31</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Name 54</t>
+          <t>Name 45</t>
         </is>
       </c>
       <c r="D14" s="4">
@@ -705,12 +705,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Name 73</t>
+          <t>Name 49</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Name 61</t>
+          <t>Name 51</t>
         </is>
       </c>
       <c r="D15" s="4">
@@ -728,12 +728,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Name 83</t>
+          <t>Name 26</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Name 49</t>
+          <t>Name 71</t>
         </is>
       </c>
       <c r="D16" s="4">

--- a/howell7.xlsx
+++ b/howell7.xlsx
@@ -506,7 +506,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>For public domain. No rights reserved. Generated on Mar 11, 2026.</t>
+          <t>For public domain. No rights reserved. Generated on Mar 18, 2026.</t>
         </is>
       </c>
     </row>
@@ -590,12 +590,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 24</t>
+          <t>Name 48</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name 21</t>
+          <t>Name 47</t>
         </is>
       </c>
       <c r="D10" s="4">
@@ -613,12 +613,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Name 59</t>
+          <t>Name 65</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Name 60</t>
+          <t>Name 63</t>
         </is>
       </c>
       <c r="D11" s="4">
@@ -636,12 +636,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Name 41</t>
+          <t>Name 80</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Name 55</t>
+          <t>Name 22</t>
         </is>
       </c>
       <c r="D12" s="4">
@@ -659,12 +659,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Name 15</t>
+          <t>Name 14</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Name 76</t>
+          <t>Name 72</t>
         </is>
       </c>
       <c r="D13" s="4">
@@ -682,12 +682,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Name 31</t>
+          <t>Name 16</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Name 45</t>
+          <t>Name 48</t>
         </is>
       </c>
       <c r="D14" s="4">
@@ -705,12 +705,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Name 49</t>
+          <t>Name 42</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Name 51</t>
+          <t>Name 55</t>
         </is>
       </c>
       <c r="D15" s="4">
@@ -728,12 +728,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Name 26</t>
+          <t>Name 53</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Name 71</t>
+          <t>Name 64</t>
         </is>
       </c>
       <c r="D16" s="4">

--- a/howell7.xlsx
+++ b/howell7.xlsx
@@ -506,7 +506,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>For public domain. No rights reserved. Generated on Mar 18, 2026.</t>
+          <t>For public domain. No rights reserved. Generated on Mar 20, 2026.</t>
         </is>
       </c>
     </row>
@@ -590,12 +590,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 48</t>
+          <t>Name 16</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name 47</t>
+          <t>Name 33</t>
         </is>
       </c>
       <c r="D10" s="4">
@@ -613,12 +613,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Name 65</t>
+          <t>Name 33</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Name 63</t>
+          <t>Name 75</t>
         </is>
       </c>
       <c r="D11" s="4">
@@ -636,12 +636,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Name 80</t>
+          <t>Name 67</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Name 22</t>
+          <t>Name 15</t>
         </is>
       </c>
       <c r="D12" s="4">
@@ -659,12 +659,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Name 14</t>
+          <t>Name 43</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Name 72</t>
+          <t>Name 83</t>
         </is>
       </c>
       <c r="D13" s="4">
@@ -682,12 +682,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Name 16</t>
+          <t>Name 45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Name 48</t>
+          <t>Name 72</t>
         </is>
       </c>
       <c r="D14" s="4">
@@ -705,12 +705,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Name 42</t>
+          <t>Name 39</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Name 55</t>
+          <t>Name 83</t>
         </is>
       </c>
       <c r="D15" s="4">
@@ -728,12 +728,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Name 53</t>
+          <t>Name 83</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Name 64</t>
+          <t>Name 15</t>
         </is>
       </c>
       <c r="D16" s="4">

--- a/howell7.xlsx
+++ b/howell7.xlsx
@@ -506,7 +506,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>For public domain. No rights reserved. Generated on Mar 20, 2026.</t>
+          <t>For public domain. No rights reserved. Generated on Apr 08, 2026.</t>
         </is>
       </c>
     </row>
@@ -590,12 +590,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 16</t>
+          <t>Name 27</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name 33</t>
+          <t>Name 55</t>
         </is>
       </c>
       <c r="D10" s="4">
@@ -613,12 +613,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Name 33</t>
+          <t>Name 18</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Name 75</t>
+          <t>Name 42</t>
         </is>
       </c>
       <c r="D11" s="4">
@@ -636,12 +636,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Name 67</t>
+          <t>Name 48</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Name 15</t>
+          <t>Name 50</t>
         </is>
       </c>
       <c r="D12" s="4">
@@ -659,12 +659,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Name 43</t>
+          <t>Name 20</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Name 83</t>
+          <t>Name 51</t>
         </is>
       </c>
       <c r="D13" s="4">
@@ -682,12 +682,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Name 45</t>
+          <t>Name 37</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Name 72</t>
+          <t>Name 15</t>
         </is>
       </c>
       <c r="D14" s="4">
@@ -705,12 +705,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Name 39</t>
+          <t>Name 61</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Name 83</t>
+          <t>Name 26</t>
         </is>
       </c>
       <c r="D15" s="4">
@@ -728,12 +728,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Name 83</t>
+          <t>Name 44</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Name 15</t>
+          <t>Name 28</t>
         </is>
       </c>
       <c r="D16" s="4">

--- a/howell7.xlsx
+++ b/howell7.xlsx
@@ -506,7 +506,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>For public domain. No rights reserved. Generated on Apr 08, 2026.</t>
+          <t>For public domain. No rights reserved. Generated on Apr 22, 2026.</t>
         </is>
       </c>
     </row>
@@ -590,12 +590,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 27</t>
+          <t>Name 60</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name 55</t>
+          <t>Name 37</t>
         </is>
       </c>
       <c r="D10" s="4">
@@ -613,12 +613,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Name 18</t>
+          <t>Name 83</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Name 42</t>
+          <t>Name 73</t>
         </is>
       </c>
       <c r="D11" s="4">
@@ -636,12 +636,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Name 48</t>
+          <t>Name 11</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Name 50</t>
+          <t>Name 33</t>
         </is>
       </c>
       <c r="D12" s="4">
@@ -659,12 +659,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Name 20</t>
+          <t>Name 88</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Name 51</t>
+          <t>Name 66</t>
         </is>
       </c>
       <c r="D13" s="4">
@@ -682,12 +682,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Name 37</t>
+          <t>Name 17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Name 15</t>
+          <t>Name 59</t>
         </is>
       </c>
       <c r="D14" s="4">
@@ -705,12 +705,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Name 61</t>
+          <t>Name 53</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Name 26</t>
+          <t>Name 11</t>
         </is>
       </c>
       <c r="D15" s="4">
@@ -728,12 +728,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Name 44</t>
+          <t>Name 82</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Name 28</t>
+          <t>Name 48</t>
         </is>
       </c>
       <c r="D16" s="4">

--- a/howell7.xlsx
+++ b/howell7.xlsx
@@ -590,20 +590,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 60</t>
+          <t>Name 77</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name 37</t>
+          <t>Name 78</t>
         </is>
       </c>
       <c r="D10" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$50,"=1",'By Board'!$O$3:$O$50)/12+SUMIF('By Board'!$E$3:$E$50,"=1",'By Board'!$P$3:$P$50)/12</f>
+        <f>SUMIF('By Board'!D3:D58,"="&amp;A10,'By Board'!Q3:Q58)/42+SUMIF('By Board'!E3:E58,"="&amp;A10,'By Board'!R3:R58)/42</f>
         <v/>
       </c>
       <c r="E10" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$50,"=1",'By Board'!$M$3:$M$50)+SUMIF('By Board'!$E$3:$E$50,"=1",'By Board'!$N$3:$N$50)</f>
+        <f>SUMIF('By Board'!D3:D58,"="&amp;A10,'By Board'!M3:M58)+SUMIF('By Board'!E3:E58,"="&amp;A10,'By Board'!N3:N58)</f>
         <v/>
       </c>
     </row>
@@ -613,20 +613,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Name 83</t>
+          <t>Name 55</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Name 73</t>
+          <t>Name 66</t>
         </is>
       </c>
       <c r="D11" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$50,"=2",'By Board'!$O$3:$O$50)/12+SUMIF('By Board'!$E$3:$E$50,"=2",'By Board'!$P$3:$P$50)/12</f>
+        <f>SUMIF('By Board'!D3:D58,"="&amp;A11,'By Board'!Q3:Q58)/42+SUMIF('By Board'!E3:E58,"="&amp;A11,'By Board'!R3:R58)/42</f>
         <v/>
       </c>
       <c r="E11" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$50,"=2",'By Board'!$M$3:$M$50)+SUMIF('By Board'!$E$3:$E$50,"=2",'By Board'!$N$3:$N$50)</f>
+        <f>SUMIF('By Board'!D3:D58,"="&amp;A11,'By Board'!M3:M58)+SUMIF('By Board'!E3:E58,"="&amp;A11,'By Board'!N3:N58)</f>
         <v/>
       </c>
     </row>
@@ -636,20 +636,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Name 11</t>
+          <t>Name 81</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Name 33</t>
+          <t>Name 57</t>
         </is>
       </c>
       <c r="D12" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$50,"=3",'By Board'!$O$3:$O$50)/12+SUMIF('By Board'!$E$3:$E$50,"=3",'By Board'!$P$3:$P$50)/12</f>
+        <f>SUMIF('By Board'!D3:D58,"="&amp;A12,'By Board'!Q3:Q58)/42+SUMIF('By Board'!E3:E58,"="&amp;A12,'By Board'!R3:R58)/42</f>
         <v/>
       </c>
       <c r="E12" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$50,"=3",'By Board'!$M$3:$M$50)+SUMIF('By Board'!$E$3:$E$50,"=3",'By Board'!$N$3:$N$50)</f>
+        <f>SUMIF('By Board'!D3:D58,"="&amp;A12,'By Board'!M3:M58)+SUMIF('By Board'!E3:E58,"="&amp;A12,'By Board'!N3:N58)</f>
         <v/>
       </c>
     </row>
@@ -659,20 +659,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Name 88</t>
+          <t>Name 42</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Name 66</t>
+          <t>Name 39</t>
         </is>
       </c>
       <c r="D13" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$50,"=4",'By Board'!$O$3:$O$50)/12+SUMIF('By Board'!$E$3:$E$50,"=4",'By Board'!$P$3:$P$50)/12</f>
+        <f>SUMIF('By Board'!D3:D58,"="&amp;A13,'By Board'!Q3:Q58)/42+SUMIF('By Board'!E3:E58,"="&amp;A13,'By Board'!R3:R58)/42</f>
         <v/>
       </c>
       <c r="E13" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$50,"=4",'By Board'!$M$3:$M$50)+SUMIF('By Board'!$E$3:$E$50,"=4",'By Board'!$N$3:$N$50)</f>
+        <f>SUMIF('By Board'!D3:D58,"="&amp;A13,'By Board'!M3:M58)+SUMIF('By Board'!E3:E58,"="&amp;A13,'By Board'!N3:N58)</f>
         <v/>
       </c>
     </row>
@@ -682,20 +682,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Name 17</t>
+          <t>Name 59</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Name 59</t>
+          <t>Name 37</t>
         </is>
       </c>
       <c r="D14" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$50,"=5",'By Board'!$O$3:$O$50)/12+SUMIF('By Board'!$E$3:$E$50,"=5",'By Board'!$P$3:$P$50)/12</f>
+        <f>SUMIF('By Board'!D3:D58,"="&amp;A14,'By Board'!Q3:Q58)/42+SUMIF('By Board'!E3:E58,"="&amp;A14,'By Board'!R3:R58)/42</f>
         <v/>
       </c>
       <c r="E14" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$50,"=5",'By Board'!$M$3:$M$50)+SUMIF('By Board'!$E$3:$E$50,"=5",'By Board'!$N$3:$N$50)</f>
+        <f>SUMIF('By Board'!D3:D58,"="&amp;A14,'By Board'!M3:M58)+SUMIF('By Board'!E3:E58,"="&amp;A14,'By Board'!N3:N58)</f>
         <v/>
       </c>
     </row>
@@ -705,20 +705,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Name 53</t>
+          <t>Name 40</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Name 11</t>
+          <t>Name 59</t>
         </is>
       </c>
       <c r="D15" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$50,"=6",'By Board'!$O$3:$O$50)/12+SUMIF('By Board'!$E$3:$E$50,"=6",'By Board'!$P$3:$P$50)/12</f>
+        <f>SUMIF('By Board'!D3:D58,"="&amp;A15,'By Board'!Q3:Q58)/42+SUMIF('By Board'!E3:E58,"="&amp;A15,'By Board'!R3:R58)/42</f>
         <v/>
       </c>
       <c r="E15" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$50,"=6",'By Board'!$M$3:$M$50)+SUMIF('By Board'!$E$3:$E$50,"=6",'By Board'!$N$3:$N$50)</f>
+        <f>SUMIF('By Board'!D3:D58,"="&amp;A15,'By Board'!M3:M58)+SUMIF('By Board'!E3:E58,"="&amp;A15,'By Board'!N3:N58)</f>
         <v/>
       </c>
     </row>
@@ -728,20 +728,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Name 82</t>
+          <t>Name 80</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Name 48</t>
+          <t>Name 73</t>
         </is>
       </c>
       <c r="D16" s="4">
-        <f>SUMIF('By Board'!$D$3:$D$50,"=7",'By Board'!$O$3:$O$50)/12+SUMIF('By Board'!$E$3:$E$50,"=7",'By Board'!$P$3:$P$50)/12</f>
+        <f>SUMIF('By Board'!D3:D58,"="&amp;A16,'By Board'!Q3:Q58)/42+SUMIF('By Board'!E3:E58,"="&amp;A16,'By Board'!R3:R58)/42</f>
         <v/>
       </c>
       <c r="E16" s="5">
-        <f>SUMIF('By Board'!$D$3:$D$50,"=7",'By Board'!$M$3:$M$50)+SUMIF('By Board'!$E$3:$E$50,"=7",'By Board'!$N$3:$N$50)</f>
+        <f>SUMIF('By Board'!D3:D58,"="&amp;A16,'By Board'!M3:M58)+SUMIF('By Board'!E3:E58,"="&amp;A16,'By Board'!N3:N58)</f>
         <v/>
       </c>
     </row>

--- a/howell7.xlsx
+++ b/howell7.xlsx
@@ -590,16 +590,16 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 77</t>
+          <t>Name 21</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name 78</t>
+          <t>Name 31</t>
         </is>
       </c>
       <c r="D10" s="4">
-        <f>SUMIF('By Board'!D3:D58,"="&amp;A10,'By Board'!Q3:Q58)/42+SUMIF('By Board'!E3:E58,"="&amp;A10,'By Board'!R3:R58)/42</f>
+        <f>SUMIF('By Board'!D3:D58,"="&amp;A10,'By Board'!Q3:Q58)/28+SUMIF('By Board'!E3:E58,"="&amp;A10,'By Board'!R3:R58)/28</f>
         <v/>
       </c>
       <c r="E10" s="5">
@@ -613,16 +613,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Name 55</t>
+          <t>Name 30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Name 66</t>
+          <t>Name 50</t>
         </is>
       </c>
       <c r="D11" s="4">
-        <f>SUMIF('By Board'!D3:D58,"="&amp;A11,'By Board'!Q3:Q58)/42+SUMIF('By Board'!E3:E58,"="&amp;A11,'By Board'!R3:R58)/42</f>
+        <f>SUMIF('By Board'!D3:D58,"="&amp;A11,'By Board'!Q3:Q58)/28+SUMIF('By Board'!E3:E58,"="&amp;A11,'By Board'!R3:R58)/28</f>
         <v/>
       </c>
       <c r="E11" s="5">
@@ -636,16 +636,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Name 81</t>
+          <t>Name 88</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Name 57</t>
+          <t>Name 31</t>
         </is>
       </c>
       <c r="D12" s="4">
-        <f>SUMIF('By Board'!D3:D58,"="&amp;A12,'By Board'!Q3:Q58)/42+SUMIF('By Board'!E3:E58,"="&amp;A12,'By Board'!R3:R58)/42</f>
+        <f>SUMIF('By Board'!D3:D58,"="&amp;A12,'By Board'!Q3:Q58)/28+SUMIF('By Board'!E3:E58,"="&amp;A12,'By Board'!R3:R58)/28</f>
         <v/>
       </c>
       <c r="E12" s="5">
@@ -659,16 +659,16 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Name 42</t>
+          <t>Name 84</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Name 39</t>
+          <t>Name 16</t>
         </is>
       </c>
       <c r="D13" s="4">
-        <f>SUMIF('By Board'!D3:D58,"="&amp;A13,'By Board'!Q3:Q58)/42+SUMIF('By Board'!E3:E58,"="&amp;A13,'By Board'!R3:R58)/42</f>
+        <f>SUMIF('By Board'!D3:D58,"="&amp;A13,'By Board'!Q3:Q58)/28+SUMIF('By Board'!E3:E58,"="&amp;A13,'By Board'!R3:R58)/28</f>
         <v/>
       </c>
       <c r="E13" s="5">
@@ -682,16 +682,16 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Name 59</t>
+          <t>Name 90</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Name 37</t>
+          <t>Name 61</t>
         </is>
       </c>
       <c r="D14" s="4">
-        <f>SUMIF('By Board'!D3:D58,"="&amp;A14,'By Board'!Q3:Q58)/42+SUMIF('By Board'!E3:E58,"="&amp;A14,'By Board'!R3:R58)/42</f>
+        <f>SUMIF('By Board'!D3:D58,"="&amp;A14,'By Board'!Q3:Q58)/28+SUMIF('By Board'!E3:E58,"="&amp;A14,'By Board'!R3:R58)/28</f>
         <v/>
       </c>
       <c r="E14" s="5">
@@ -705,16 +705,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Name 40</t>
+          <t>Name 75</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Name 59</t>
+          <t>Name 47</t>
         </is>
       </c>
       <c r="D15" s="4">
-        <f>SUMIF('By Board'!D3:D58,"="&amp;A15,'By Board'!Q3:Q58)/42+SUMIF('By Board'!E3:E58,"="&amp;A15,'By Board'!R3:R58)/42</f>
+        <f>SUMIF('By Board'!D3:D58,"="&amp;A15,'By Board'!Q3:Q58)/28+SUMIF('By Board'!E3:E58,"="&amp;A15,'By Board'!R3:R58)/28</f>
         <v/>
       </c>
       <c r="E15" s="5">
@@ -728,16 +728,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Name 80</t>
+          <t>Name 30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Name 73</t>
+          <t>Name 21</t>
         </is>
       </c>
       <c r="D16" s="4">
-        <f>SUMIF('By Board'!D3:D58,"="&amp;A16,'By Board'!Q3:Q58)/42+SUMIF('By Board'!E3:E58,"="&amp;A16,'By Board'!R3:R58)/42</f>
+        <f>SUMIF('By Board'!D3:D58,"="&amp;A16,'By Board'!Q3:Q58)/28+SUMIF('By Board'!E3:E58,"="&amp;A16,'By Board'!R3:R58)/28</f>
         <v/>
       </c>
       <c r="E16" s="5">

--- a/howell7.xlsx
+++ b/howell7.xlsx
@@ -506,7 +506,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>For public domain. No rights reserved. Generated on Apr 22, 2026.</t>
+          <t>For public domain. No rights reserved. Generated on Apr 23, 2026.</t>
         </is>
       </c>
     </row>
@@ -590,12 +590,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 21</t>
+          <t>Name 48</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name 31</t>
+          <t>Name 82</t>
         </is>
       </c>
       <c r="D10" s="4">
@@ -613,12 +613,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Name 30</t>
+          <t>Name 32</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Name 50</t>
+          <t>Name 84</t>
         </is>
       </c>
       <c r="D11" s="4">
@@ -636,12 +636,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Name 88</t>
+          <t>Name 62</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Name 31</t>
+          <t>Name 55</t>
         </is>
       </c>
       <c r="D12" s="4">
@@ -659,12 +659,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Name 84</t>
+          <t>Name 82</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Name 16</t>
+          <t>Name 63</t>
         </is>
       </c>
       <c r="D13" s="4">
@@ -682,12 +682,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Name 90</t>
+          <t>Name 79</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Name 61</t>
+          <t>Name 31</t>
         </is>
       </c>
       <c r="D14" s="4">
@@ -705,12 +705,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Name 75</t>
+          <t>Name 46</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Name 47</t>
+          <t>Name 58</t>
         </is>
       </c>
       <c r="D15" s="4">
@@ -728,12 +728,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Name 30</t>
+          <t>Name 29</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Name 21</t>
+          <t>Name 77</t>
         </is>
       </c>
       <c r="D16" s="4">
@@ -1026,27 +1026,27 @@
         <v/>
       </c>
       <c r="U3" s="14">
-        <f>IF(ISNUMBER(S3),IF(ISNUMBER(S4),IF(S3&gt;S4,1.0,IF(S3=S4,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S3),IF(ISNUMBER(S4),IF(S3&gt;S4,1.0,IF(S3=S4,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V3">
-        <f>IF(ISNUMBER(S3),IF(ISNUMBER(S5),IF(S3&gt;S5,1.0,IF(S3=S5,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S3),IF(ISNUMBER(S5),IF(S3&gt;S5,1.0,IF(S3=S5,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W3">
-        <f>IF(ISNUMBER(S3),IF(ISNUMBER(S6),IF(S3&gt;S6,1.0,IF(S3=S6,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S3),IF(ISNUMBER(S6),IF(S3&gt;S6,1.0,IF(S3=S6,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X3">
-        <f>IF(ISNUMBER(T3),IF(ISNUMBER(T4),IF(T3&gt;T4,1.0,IF(T3=T4,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T3),IF(ISNUMBER(T4),IF(T3&gt;T4,1.0,IF(T3=T4,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>IF(ISNUMBER(T3),IF(ISNUMBER(T5),IF(T3&gt;T5,1.0,IF(T3=T5,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T3),IF(ISNUMBER(T5),IF(T3&gt;T5,1.0,IF(T3=T5,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z3">
-        <f>IF(ISNUMBER(T3),IF(ISNUMBER(T6),IF(T3&gt;T6,1.0,IF(T3=T6,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T3),IF(ISNUMBER(T6),IF(T3&gt;T6,1.0,IF(T3=T6,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA3" s="14">
@@ -1152,27 +1152,27 @@
         <v/>
       </c>
       <c r="U4" s="14">
-        <f>IF(ISNUMBER(S4),IF(ISNUMBER(S3),IF(S4&gt;S3,1.0,IF(S4=S3,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S4),IF(ISNUMBER(S3),IF(S4&gt;S3,1.0,IF(S4=S3,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V4">
-        <f>IF(ISNUMBER(S4),IF(ISNUMBER(S5),IF(S4&gt;S5,1.0,IF(S4=S5,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S4),IF(ISNUMBER(S5),IF(S4&gt;S5,1.0,IF(S4=S5,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W4">
-        <f>IF(ISNUMBER(S4),IF(ISNUMBER(S6),IF(S4&gt;S6,1.0,IF(S4=S6,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S4),IF(ISNUMBER(S6),IF(S4&gt;S6,1.0,IF(S4=S6,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X4">
-        <f>IF(ISNUMBER(T4),IF(ISNUMBER(T3),IF(T4&gt;T3,1.0,IF(T4=T3,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T4),IF(ISNUMBER(T3),IF(T4&gt;T3,1.0,IF(T4=T3,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>IF(ISNUMBER(T4),IF(ISNUMBER(T5),IF(T4&gt;T5,1.0,IF(T4=T5,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T4),IF(ISNUMBER(T5),IF(T4&gt;T5,1.0,IF(T4=T5,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z4">
-        <f>IF(ISNUMBER(T4),IF(ISNUMBER(T6),IF(T4&gt;T6,1.0,IF(T4=T6,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T4),IF(ISNUMBER(T6),IF(T4&gt;T6,1.0,IF(T4=T6,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA4" s="14">
@@ -1278,27 +1278,27 @@
         <v/>
       </c>
       <c r="U5" s="14">
-        <f>IF(ISNUMBER(S5),IF(ISNUMBER(S3),IF(S5&gt;S3,1.0,IF(S5=S3,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S5),IF(ISNUMBER(S3),IF(S5&gt;S3,1.0,IF(S5=S3,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V5">
-        <f>IF(ISNUMBER(S5),IF(ISNUMBER(S4),IF(S5&gt;S4,1.0,IF(S5=S4,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S5),IF(ISNUMBER(S4),IF(S5&gt;S4,1.0,IF(S5=S4,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W5">
-        <f>IF(ISNUMBER(S5),IF(ISNUMBER(S6),IF(S5&gt;S6,1.0,IF(S5=S6,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S5),IF(ISNUMBER(S6),IF(S5&gt;S6,1.0,IF(S5=S6,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X5">
-        <f>IF(ISNUMBER(T5),IF(ISNUMBER(T3),IF(T5&gt;T3,1.0,IF(T5=T3,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T5),IF(ISNUMBER(T3),IF(T5&gt;T3,1.0,IF(T5=T3,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>IF(ISNUMBER(T5),IF(ISNUMBER(T4),IF(T5&gt;T4,1.0,IF(T5=T4,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T5),IF(ISNUMBER(T4),IF(T5&gt;T4,1.0,IF(T5=T4,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z5">
-        <f>IF(ISNUMBER(T5),IF(ISNUMBER(T6),IF(T5&gt;T6,1.0,IF(T5=T6,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T5),IF(ISNUMBER(T6),IF(T5&gt;T6,1.0,IF(T5=T6,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA5" s="14">
@@ -1405,27 +1405,27 @@
         <v/>
       </c>
       <c r="U6" s="21">
-        <f>IF(ISNUMBER(S6),IF(ISNUMBER(S3),IF(S6&gt;S3,1.0,IF(S6=S3,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S6),IF(ISNUMBER(S3),IF(S6&gt;S3,1.0,IF(S6=S3,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V6" s="15">
-        <f>IF(ISNUMBER(S6),IF(ISNUMBER(S4),IF(S6&gt;S4,1.0,IF(S6=S4,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S6),IF(ISNUMBER(S4),IF(S6&gt;S4,1.0,IF(S6=S4,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W6" s="15">
-        <f>IF(ISNUMBER(S6),IF(ISNUMBER(S5),IF(S6&gt;S5,1.0,IF(S6=S5,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S6),IF(ISNUMBER(S5),IF(S6&gt;S5,1.0,IF(S6=S5,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X6" s="15">
-        <f>IF(ISNUMBER(T6),IF(ISNUMBER(T3),IF(T6&gt;T3,1.0,IF(T6=T3,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T6),IF(ISNUMBER(T3),IF(T6&gt;T3,1.0,IF(T6=T3,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y6" s="15">
-        <f>IF(ISNUMBER(T6),IF(ISNUMBER(T4),IF(T6&gt;T4,1.0,IF(T6=T4,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T6),IF(ISNUMBER(T4),IF(T6&gt;T4,1.0,IF(T6=T4,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z6" s="15">
-        <f>IF(ISNUMBER(T6),IF(ISNUMBER(T5),IF(T6&gt;T5,1.0,IF(T6=T5,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T6),IF(ISNUMBER(T5),IF(T6&gt;T5,1.0,IF(T6=T5,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA6" s="21">
@@ -1534,27 +1534,27 @@
         <v/>
       </c>
       <c r="U7" s="14">
-        <f>IF(ISNUMBER(S7),IF(ISNUMBER(S8),IF(S7&gt;S8,1.0,IF(S7=S8,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S7),IF(ISNUMBER(S8),IF(S7&gt;S8,1.0,IF(S7=S8,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V7">
-        <f>IF(ISNUMBER(S7),IF(ISNUMBER(S9),IF(S7&gt;S9,1.0,IF(S7=S9,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S7),IF(ISNUMBER(S9),IF(S7&gt;S9,1.0,IF(S7=S9,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W7">
-        <f>IF(ISNUMBER(S7),IF(ISNUMBER(S10),IF(S7&gt;S10,1.0,IF(S7=S10,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S7),IF(ISNUMBER(S10),IF(S7&gt;S10,1.0,IF(S7=S10,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X7">
-        <f>IF(ISNUMBER(T7),IF(ISNUMBER(T8),IF(T7&gt;T8,1.0,IF(T7=T8,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T7),IF(ISNUMBER(T8),IF(T7&gt;T8,1.0,IF(T7=T8,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>IF(ISNUMBER(T7),IF(ISNUMBER(T9),IF(T7&gt;T9,1.0,IF(T7=T9,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T7),IF(ISNUMBER(T9),IF(T7&gt;T9,1.0,IF(T7=T9,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z7">
-        <f>IF(ISNUMBER(T7),IF(ISNUMBER(T10),IF(T7&gt;T10,1.0,IF(T7=T10,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T7),IF(ISNUMBER(T10),IF(T7&gt;T10,1.0,IF(T7=T10,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA7" s="14">
@@ -1660,27 +1660,27 @@
         <v/>
       </c>
       <c r="U8" s="14">
-        <f>IF(ISNUMBER(S8),IF(ISNUMBER(S7),IF(S8&gt;S7,1.0,IF(S8=S7,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S8),IF(ISNUMBER(S7),IF(S8&gt;S7,1.0,IF(S8=S7,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V8">
-        <f>IF(ISNUMBER(S8),IF(ISNUMBER(S9),IF(S8&gt;S9,1.0,IF(S8=S9,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S8),IF(ISNUMBER(S9),IF(S8&gt;S9,1.0,IF(S8=S9,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W8">
-        <f>IF(ISNUMBER(S8),IF(ISNUMBER(S10),IF(S8&gt;S10,1.0,IF(S8=S10,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S8),IF(ISNUMBER(S10),IF(S8&gt;S10,1.0,IF(S8=S10,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X8">
-        <f>IF(ISNUMBER(T8),IF(ISNUMBER(T7),IF(T8&gt;T7,1.0,IF(T8=T7,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T8),IF(ISNUMBER(T7),IF(T8&gt;T7,1.0,IF(T8=T7,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>IF(ISNUMBER(T8),IF(ISNUMBER(T9),IF(T8&gt;T9,1.0,IF(T8=T9,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T8),IF(ISNUMBER(T9),IF(T8&gt;T9,1.0,IF(T8=T9,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z8">
-        <f>IF(ISNUMBER(T8),IF(ISNUMBER(T10),IF(T8&gt;T10,1.0,IF(T8=T10,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T8),IF(ISNUMBER(T10),IF(T8&gt;T10,1.0,IF(T8=T10,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA8" s="14">
@@ -1786,27 +1786,27 @@
         <v/>
       </c>
       <c r="U9" s="14">
-        <f>IF(ISNUMBER(S9),IF(ISNUMBER(S7),IF(S9&gt;S7,1.0,IF(S9=S7,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S9),IF(ISNUMBER(S7),IF(S9&gt;S7,1.0,IF(S9=S7,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V9">
-        <f>IF(ISNUMBER(S9),IF(ISNUMBER(S8),IF(S9&gt;S8,1.0,IF(S9=S8,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S9),IF(ISNUMBER(S8),IF(S9&gt;S8,1.0,IF(S9=S8,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W9">
-        <f>IF(ISNUMBER(S9),IF(ISNUMBER(S10),IF(S9&gt;S10,1.0,IF(S9=S10,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S9),IF(ISNUMBER(S10),IF(S9&gt;S10,1.0,IF(S9=S10,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X9">
-        <f>IF(ISNUMBER(T9),IF(ISNUMBER(T7),IF(T9&gt;T7,1.0,IF(T9=T7,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T9),IF(ISNUMBER(T7),IF(T9&gt;T7,1.0,IF(T9=T7,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>IF(ISNUMBER(T9),IF(ISNUMBER(T8),IF(T9&gt;T8,1.0,IF(T9=T8,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T9),IF(ISNUMBER(T8),IF(T9&gt;T8,1.0,IF(T9=T8,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z9">
-        <f>IF(ISNUMBER(T9),IF(ISNUMBER(T10),IF(T9&gt;T10,1.0,IF(T9=T10,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T9),IF(ISNUMBER(T10),IF(T9&gt;T10,1.0,IF(T9=T10,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA9" s="14">
@@ -1913,27 +1913,27 @@
         <v/>
       </c>
       <c r="U10" s="21">
-        <f>IF(ISNUMBER(S10),IF(ISNUMBER(S7),IF(S10&gt;S7,1.0,IF(S10=S7,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S10),IF(ISNUMBER(S7),IF(S10&gt;S7,1.0,IF(S10=S7,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V10" s="15">
-        <f>IF(ISNUMBER(S10),IF(ISNUMBER(S8),IF(S10&gt;S8,1.0,IF(S10=S8,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S10),IF(ISNUMBER(S8),IF(S10&gt;S8,1.0,IF(S10=S8,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W10" s="15">
-        <f>IF(ISNUMBER(S10),IF(ISNUMBER(S9),IF(S10&gt;S9,1.0,IF(S10=S9,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S10),IF(ISNUMBER(S9),IF(S10&gt;S9,1.0,IF(S10=S9,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X10" s="15">
-        <f>IF(ISNUMBER(T10),IF(ISNUMBER(T7),IF(T10&gt;T7,1.0,IF(T10=T7,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T10),IF(ISNUMBER(T7),IF(T10&gt;T7,1.0,IF(T10=T7,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y10" s="15">
-        <f>IF(ISNUMBER(T10),IF(ISNUMBER(T8),IF(T10&gt;T8,1.0,IF(T10=T8,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T10),IF(ISNUMBER(T8),IF(T10&gt;T8,1.0,IF(T10=T8,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z10" s="15">
-        <f>IF(ISNUMBER(T10),IF(ISNUMBER(T9),IF(T10&gt;T9,1.0,IF(T10=T9,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T10),IF(ISNUMBER(T9),IF(T10&gt;T9,1.0,IF(T10=T9,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA10" s="21">
@@ -2042,27 +2042,27 @@
         <v/>
       </c>
       <c r="U11" s="14">
-        <f>IF(ISNUMBER(S11),IF(ISNUMBER(S12),IF(S11&gt;S12,1.0,IF(S11=S12,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S11),IF(ISNUMBER(S12),IF(S11&gt;S12,1.0,IF(S11=S12,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V11">
-        <f>IF(ISNUMBER(S11),IF(ISNUMBER(S13),IF(S11&gt;S13,1.0,IF(S11=S13,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S11),IF(ISNUMBER(S13),IF(S11&gt;S13,1.0,IF(S11=S13,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W11">
-        <f>IF(ISNUMBER(S11),IF(ISNUMBER(S14),IF(S11&gt;S14,1.0,IF(S11=S14,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S11),IF(ISNUMBER(S14),IF(S11&gt;S14,1.0,IF(S11=S14,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X11">
-        <f>IF(ISNUMBER(T11),IF(ISNUMBER(T12),IF(T11&gt;T12,1.0,IF(T11=T12,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T11),IF(ISNUMBER(T12),IF(T11&gt;T12,1.0,IF(T11=T12,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>IF(ISNUMBER(T11),IF(ISNUMBER(T13),IF(T11&gt;T13,1.0,IF(T11=T13,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T11),IF(ISNUMBER(T13),IF(T11&gt;T13,1.0,IF(T11=T13,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z11">
-        <f>IF(ISNUMBER(T11),IF(ISNUMBER(T14),IF(T11&gt;T14,1.0,IF(T11=T14,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T11),IF(ISNUMBER(T14),IF(T11&gt;T14,1.0,IF(T11=T14,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA11" s="14">
@@ -2168,27 +2168,27 @@
         <v/>
       </c>
       <c r="U12" s="14">
-        <f>IF(ISNUMBER(S12),IF(ISNUMBER(S11),IF(S12&gt;S11,1.0,IF(S12=S11,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S12),IF(ISNUMBER(S11),IF(S12&gt;S11,1.0,IF(S12=S11,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V12">
-        <f>IF(ISNUMBER(S12),IF(ISNUMBER(S13),IF(S12&gt;S13,1.0,IF(S12=S13,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S12),IF(ISNUMBER(S13),IF(S12&gt;S13,1.0,IF(S12=S13,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W12">
-        <f>IF(ISNUMBER(S12),IF(ISNUMBER(S14),IF(S12&gt;S14,1.0,IF(S12=S14,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S12),IF(ISNUMBER(S14),IF(S12&gt;S14,1.0,IF(S12=S14,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X12">
-        <f>IF(ISNUMBER(T12),IF(ISNUMBER(T11),IF(T12&gt;T11,1.0,IF(T12=T11,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T12),IF(ISNUMBER(T11),IF(T12&gt;T11,1.0,IF(T12=T11,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>IF(ISNUMBER(T12),IF(ISNUMBER(T13),IF(T12&gt;T13,1.0,IF(T12=T13,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T12),IF(ISNUMBER(T13),IF(T12&gt;T13,1.0,IF(T12=T13,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z12">
-        <f>IF(ISNUMBER(T12),IF(ISNUMBER(T14),IF(T12&gt;T14,1.0,IF(T12=T14,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T12),IF(ISNUMBER(T14),IF(T12&gt;T14,1.0,IF(T12=T14,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA12" s="14">
@@ -2294,27 +2294,27 @@
         <v/>
       </c>
       <c r="U13" s="14">
-        <f>IF(ISNUMBER(S13),IF(ISNUMBER(S11),IF(S13&gt;S11,1.0,IF(S13=S11,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S13),IF(ISNUMBER(S11),IF(S13&gt;S11,1.0,IF(S13=S11,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V13">
-        <f>IF(ISNUMBER(S13),IF(ISNUMBER(S12),IF(S13&gt;S12,1.0,IF(S13=S12,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S13),IF(ISNUMBER(S12),IF(S13&gt;S12,1.0,IF(S13=S12,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W13">
-        <f>IF(ISNUMBER(S13),IF(ISNUMBER(S14),IF(S13&gt;S14,1.0,IF(S13=S14,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S13),IF(ISNUMBER(S14),IF(S13&gt;S14,1.0,IF(S13=S14,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X13">
-        <f>IF(ISNUMBER(T13),IF(ISNUMBER(T11),IF(T13&gt;T11,1.0,IF(T13=T11,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T13),IF(ISNUMBER(T11),IF(T13&gt;T11,1.0,IF(T13=T11,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>IF(ISNUMBER(T13),IF(ISNUMBER(T12),IF(T13&gt;T12,1.0,IF(T13=T12,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T13),IF(ISNUMBER(T12),IF(T13&gt;T12,1.0,IF(T13=T12,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z13">
-        <f>IF(ISNUMBER(T13),IF(ISNUMBER(T14),IF(T13&gt;T14,1.0,IF(T13=T14,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T13),IF(ISNUMBER(T14),IF(T13&gt;T14,1.0,IF(T13=T14,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA13" s="14">
@@ -2421,27 +2421,27 @@
         <v/>
       </c>
       <c r="U14" s="21">
-        <f>IF(ISNUMBER(S14),IF(ISNUMBER(S11),IF(S14&gt;S11,1.0,IF(S14=S11,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S14),IF(ISNUMBER(S11),IF(S14&gt;S11,1.0,IF(S14=S11,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V14" s="15">
-        <f>IF(ISNUMBER(S14),IF(ISNUMBER(S12),IF(S14&gt;S12,1.0,IF(S14=S12,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S14),IF(ISNUMBER(S12),IF(S14&gt;S12,1.0,IF(S14=S12,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W14" s="15">
-        <f>IF(ISNUMBER(S14),IF(ISNUMBER(S13),IF(S14&gt;S13,1.0,IF(S14=S13,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S14),IF(ISNUMBER(S13),IF(S14&gt;S13,1.0,IF(S14=S13,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X14" s="15">
-        <f>IF(ISNUMBER(T14),IF(ISNUMBER(T11),IF(T14&gt;T11,1.0,IF(T14=T11,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T14),IF(ISNUMBER(T11),IF(T14&gt;T11,1.0,IF(T14=T11,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y14" s="15">
-        <f>IF(ISNUMBER(T14),IF(ISNUMBER(T12),IF(T14&gt;T12,1.0,IF(T14=T12,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T14),IF(ISNUMBER(T12),IF(T14&gt;T12,1.0,IF(T14=T12,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z14" s="15">
-        <f>IF(ISNUMBER(T14),IF(ISNUMBER(T13),IF(T14&gt;T13,1.0,IF(T14=T13,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T14),IF(ISNUMBER(T13),IF(T14&gt;T13,1.0,IF(T14=T13,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA14" s="21">
@@ -2550,27 +2550,27 @@
         <v/>
       </c>
       <c r="U15" s="14">
-        <f>IF(ISNUMBER(S15),IF(ISNUMBER(S16),IF(S15&gt;S16,1.0,IF(S15=S16,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S15),IF(ISNUMBER(S16),IF(S15&gt;S16,1.0,IF(S15=S16,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V15">
-        <f>IF(ISNUMBER(S15),IF(ISNUMBER(S17),IF(S15&gt;S17,1.0,IF(S15=S17,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S15),IF(ISNUMBER(S17),IF(S15&gt;S17,1.0,IF(S15=S17,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W15">
-        <f>IF(ISNUMBER(S15),IF(ISNUMBER(S18),IF(S15&gt;S18,1.0,IF(S15=S18,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S15),IF(ISNUMBER(S18),IF(S15&gt;S18,1.0,IF(S15=S18,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X15">
-        <f>IF(ISNUMBER(T15),IF(ISNUMBER(T16),IF(T15&gt;T16,1.0,IF(T15=T16,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T15),IF(ISNUMBER(T16),IF(T15&gt;T16,1.0,IF(T15=T16,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>IF(ISNUMBER(T15),IF(ISNUMBER(T17),IF(T15&gt;T17,1.0,IF(T15=T17,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T15),IF(ISNUMBER(T17),IF(T15&gt;T17,1.0,IF(T15=T17,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z15">
-        <f>IF(ISNUMBER(T15),IF(ISNUMBER(T18),IF(T15&gt;T18,1.0,IF(T15=T18,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T15),IF(ISNUMBER(T18),IF(T15&gt;T18,1.0,IF(T15=T18,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA15" s="14">
@@ -2676,27 +2676,27 @@
         <v/>
       </c>
       <c r="U16" s="14">
-        <f>IF(ISNUMBER(S16),IF(ISNUMBER(S15),IF(S16&gt;S15,1.0,IF(S16=S15,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S16),IF(ISNUMBER(S15),IF(S16&gt;S15,1.0,IF(S16=S15,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V16">
-        <f>IF(ISNUMBER(S16),IF(ISNUMBER(S17),IF(S16&gt;S17,1.0,IF(S16=S17,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S16),IF(ISNUMBER(S17),IF(S16&gt;S17,1.0,IF(S16=S17,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W16">
-        <f>IF(ISNUMBER(S16),IF(ISNUMBER(S18),IF(S16&gt;S18,1.0,IF(S16=S18,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S16),IF(ISNUMBER(S18),IF(S16&gt;S18,1.0,IF(S16=S18,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X16">
-        <f>IF(ISNUMBER(T16),IF(ISNUMBER(T15),IF(T16&gt;T15,1.0,IF(T16=T15,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T16),IF(ISNUMBER(T15),IF(T16&gt;T15,1.0,IF(T16=T15,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>IF(ISNUMBER(T16),IF(ISNUMBER(T17),IF(T16&gt;T17,1.0,IF(T16=T17,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T16),IF(ISNUMBER(T17),IF(T16&gt;T17,1.0,IF(T16=T17,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z16">
-        <f>IF(ISNUMBER(T16),IF(ISNUMBER(T18),IF(T16&gt;T18,1.0,IF(T16=T18,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T16),IF(ISNUMBER(T18),IF(T16&gt;T18,1.0,IF(T16=T18,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA16" s="14">
@@ -2802,27 +2802,27 @@
         <v/>
       </c>
       <c r="U17" s="14">
-        <f>IF(ISNUMBER(S17),IF(ISNUMBER(S15),IF(S17&gt;S15,1.0,IF(S17=S15,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S17),IF(ISNUMBER(S15),IF(S17&gt;S15,1.0,IF(S17=S15,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V17">
-        <f>IF(ISNUMBER(S17),IF(ISNUMBER(S16),IF(S17&gt;S16,1.0,IF(S17=S16,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S17),IF(ISNUMBER(S16),IF(S17&gt;S16,1.0,IF(S17=S16,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W17">
-        <f>IF(ISNUMBER(S17),IF(ISNUMBER(S18),IF(S17&gt;S18,1.0,IF(S17=S18,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S17),IF(ISNUMBER(S18),IF(S17&gt;S18,1.0,IF(S17=S18,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X17">
-        <f>IF(ISNUMBER(T17),IF(ISNUMBER(T15),IF(T17&gt;T15,1.0,IF(T17=T15,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T17),IF(ISNUMBER(T15),IF(T17&gt;T15,1.0,IF(T17=T15,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>IF(ISNUMBER(T17),IF(ISNUMBER(T16),IF(T17&gt;T16,1.0,IF(T17=T16,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T17),IF(ISNUMBER(T16),IF(T17&gt;T16,1.0,IF(T17=T16,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z17">
-        <f>IF(ISNUMBER(T17),IF(ISNUMBER(T18),IF(T17&gt;T18,1.0,IF(T17=T18,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T17),IF(ISNUMBER(T18),IF(T17&gt;T18,1.0,IF(T17=T18,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA17" s="14">
@@ -2929,27 +2929,27 @@
         <v/>
       </c>
       <c r="U18" s="21">
-        <f>IF(ISNUMBER(S18),IF(ISNUMBER(S15),IF(S18&gt;S15,1.0,IF(S18=S15,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S18),IF(ISNUMBER(S15),IF(S18&gt;S15,1.0,IF(S18=S15,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V18" s="15">
-        <f>IF(ISNUMBER(S18),IF(ISNUMBER(S16),IF(S18&gt;S16,1.0,IF(S18=S16,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S18),IF(ISNUMBER(S16),IF(S18&gt;S16,1.0,IF(S18=S16,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W18" s="15">
-        <f>IF(ISNUMBER(S18),IF(ISNUMBER(S17),IF(S18&gt;S17,1.0,IF(S18=S17,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S18),IF(ISNUMBER(S17),IF(S18&gt;S17,1.0,IF(S18=S17,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X18" s="15">
-        <f>IF(ISNUMBER(T18),IF(ISNUMBER(T15),IF(T18&gt;T15,1.0,IF(T18=T15,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T18),IF(ISNUMBER(T15),IF(T18&gt;T15,1.0,IF(T18=T15,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y18" s="15">
-        <f>IF(ISNUMBER(T18),IF(ISNUMBER(T16),IF(T18&gt;T16,1.0,IF(T18=T16,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T18),IF(ISNUMBER(T16),IF(T18&gt;T16,1.0,IF(T18=T16,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z18" s="15">
-        <f>IF(ISNUMBER(T18),IF(ISNUMBER(T17),IF(T18&gt;T17,1.0,IF(T18=T17,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T18),IF(ISNUMBER(T17),IF(T18&gt;T17,1.0,IF(T18=T17,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA18" s="21">
@@ -3058,27 +3058,27 @@
         <v/>
       </c>
       <c r="U19" s="14">
-        <f>IF(ISNUMBER(S19),IF(ISNUMBER(S20),IF(S19&gt;S20,1.0,IF(S19=S20,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S19),IF(ISNUMBER(S20),IF(S19&gt;S20,1.0,IF(S19=S20,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V19">
-        <f>IF(ISNUMBER(S19),IF(ISNUMBER(S21),IF(S19&gt;S21,1.0,IF(S19=S21,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S19),IF(ISNUMBER(S21),IF(S19&gt;S21,1.0,IF(S19=S21,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W19">
-        <f>IF(ISNUMBER(S19),IF(ISNUMBER(S22),IF(S19&gt;S22,1.0,IF(S19=S22,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S19),IF(ISNUMBER(S22),IF(S19&gt;S22,1.0,IF(S19=S22,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X19">
-        <f>IF(ISNUMBER(T19),IF(ISNUMBER(T20),IF(T19&gt;T20,1.0,IF(T19=T20,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T19),IF(ISNUMBER(T20),IF(T19&gt;T20,1.0,IF(T19=T20,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>IF(ISNUMBER(T19),IF(ISNUMBER(T21),IF(T19&gt;T21,1.0,IF(T19=T21,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T19),IF(ISNUMBER(T21),IF(T19&gt;T21,1.0,IF(T19=T21,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z19">
-        <f>IF(ISNUMBER(T19),IF(ISNUMBER(T22),IF(T19&gt;T22,1.0,IF(T19=T22,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T19),IF(ISNUMBER(T22),IF(T19&gt;T22,1.0,IF(T19=T22,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA19" s="14">
@@ -3184,27 +3184,27 @@
         <v/>
       </c>
       <c r="U20" s="14">
-        <f>IF(ISNUMBER(S20),IF(ISNUMBER(S19),IF(S20&gt;S19,1.0,IF(S20=S19,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S20),IF(ISNUMBER(S19),IF(S20&gt;S19,1.0,IF(S20=S19,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V20">
-        <f>IF(ISNUMBER(S20),IF(ISNUMBER(S21),IF(S20&gt;S21,1.0,IF(S20=S21,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S20),IF(ISNUMBER(S21),IF(S20&gt;S21,1.0,IF(S20=S21,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W20">
-        <f>IF(ISNUMBER(S20),IF(ISNUMBER(S22),IF(S20&gt;S22,1.0,IF(S20=S22,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S20),IF(ISNUMBER(S22),IF(S20&gt;S22,1.0,IF(S20=S22,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X20">
-        <f>IF(ISNUMBER(T20),IF(ISNUMBER(T19),IF(T20&gt;T19,1.0,IF(T20=T19,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T20),IF(ISNUMBER(T19),IF(T20&gt;T19,1.0,IF(T20=T19,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>IF(ISNUMBER(T20),IF(ISNUMBER(T21),IF(T20&gt;T21,1.0,IF(T20=T21,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T20),IF(ISNUMBER(T21),IF(T20&gt;T21,1.0,IF(T20=T21,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z20">
-        <f>IF(ISNUMBER(T20),IF(ISNUMBER(T22),IF(T20&gt;T22,1.0,IF(T20=T22,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T20),IF(ISNUMBER(T22),IF(T20&gt;T22,1.0,IF(T20=T22,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA20" s="14">
@@ -3310,27 +3310,27 @@
         <v/>
       </c>
       <c r="U21" s="14">
-        <f>IF(ISNUMBER(S21),IF(ISNUMBER(S19),IF(S21&gt;S19,1.0,IF(S21=S19,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S21),IF(ISNUMBER(S19),IF(S21&gt;S19,1.0,IF(S21=S19,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V21">
-        <f>IF(ISNUMBER(S21),IF(ISNUMBER(S20),IF(S21&gt;S20,1.0,IF(S21=S20,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S21),IF(ISNUMBER(S20),IF(S21&gt;S20,1.0,IF(S21=S20,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W21">
-        <f>IF(ISNUMBER(S21),IF(ISNUMBER(S22),IF(S21&gt;S22,1.0,IF(S21=S22,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S21),IF(ISNUMBER(S22),IF(S21&gt;S22,1.0,IF(S21=S22,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X21">
-        <f>IF(ISNUMBER(T21),IF(ISNUMBER(T19),IF(T21&gt;T19,1.0,IF(T21=T19,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T21),IF(ISNUMBER(T19),IF(T21&gt;T19,1.0,IF(T21=T19,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>IF(ISNUMBER(T21),IF(ISNUMBER(T20),IF(T21&gt;T20,1.0,IF(T21=T20,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T21),IF(ISNUMBER(T20),IF(T21&gt;T20,1.0,IF(T21=T20,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z21">
-        <f>IF(ISNUMBER(T21),IF(ISNUMBER(T22),IF(T21&gt;T22,1.0,IF(T21=T22,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T21),IF(ISNUMBER(T22),IF(T21&gt;T22,1.0,IF(T21=T22,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA21" s="14">
@@ -3437,27 +3437,27 @@
         <v/>
       </c>
       <c r="U22" s="21">
-        <f>IF(ISNUMBER(S22),IF(ISNUMBER(S19),IF(S22&gt;S19,1.0,IF(S22=S19,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S22),IF(ISNUMBER(S19),IF(S22&gt;S19,1.0,IF(S22=S19,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V22" s="15">
-        <f>IF(ISNUMBER(S22),IF(ISNUMBER(S20),IF(S22&gt;S20,1.0,IF(S22=S20,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S22),IF(ISNUMBER(S20),IF(S22&gt;S20,1.0,IF(S22=S20,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W22" s="15">
-        <f>IF(ISNUMBER(S22),IF(ISNUMBER(S21),IF(S22&gt;S21,1.0,IF(S22=S21,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S22),IF(ISNUMBER(S21),IF(S22&gt;S21,1.0,IF(S22=S21,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X22" s="15">
-        <f>IF(ISNUMBER(T22),IF(ISNUMBER(T19),IF(T22&gt;T19,1.0,IF(T22=T19,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T22),IF(ISNUMBER(T19),IF(T22&gt;T19,1.0,IF(T22=T19,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y22" s="15">
-        <f>IF(ISNUMBER(T22),IF(ISNUMBER(T20),IF(T22&gt;T20,1.0,IF(T22=T20,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T22),IF(ISNUMBER(T20),IF(T22&gt;T20,1.0,IF(T22=T20,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z22" s="15">
-        <f>IF(ISNUMBER(T22),IF(ISNUMBER(T21),IF(T22&gt;T21,1.0,IF(T22=T21,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T22),IF(ISNUMBER(T21),IF(T22&gt;T21,1.0,IF(T22=T21,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA22" s="21">
@@ -3566,27 +3566,27 @@
         <v/>
       </c>
       <c r="U23" s="14">
-        <f>IF(ISNUMBER(S23),IF(ISNUMBER(S24),IF(S23&gt;S24,1.0,IF(S23=S24,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S23),IF(ISNUMBER(S24),IF(S23&gt;S24,1.0,IF(S23=S24,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V23">
-        <f>IF(ISNUMBER(S23),IF(ISNUMBER(S25),IF(S23&gt;S25,1.0,IF(S23=S25,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S23),IF(ISNUMBER(S25),IF(S23&gt;S25,1.0,IF(S23=S25,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W23">
-        <f>IF(ISNUMBER(S23),IF(ISNUMBER(S26),IF(S23&gt;S26,1.0,IF(S23=S26,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S23),IF(ISNUMBER(S26),IF(S23&gt;S26,1.0,IF(S23=S26,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X23">
-        <f>IF(ISNUMBER(T23),IF(ISNUMBER(T24),IF(T23&gt;T24,1.0,IF(T23=T24,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T23),IF(ISNUMBER(T24),IF(T23&gt;T24,1.0,IF(T23=T24,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>IF(ISNUMBER(T23),IF(ISNUMBER(T25),IF(T23&gt;T25,1.0,IF(T23=T25,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T23),IF(ISNUMBER(T25),IF(T23&gt;T25,1.0,IF(T23=T25,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z23">
-        <f>IF(ISNUMBER(T23),IF(ISNUMBER(T26),IF(T23&gt;T26,1.0,IF(T23=T26,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T23),IF(ISNUMBER(T26),IF(T23&gt;T26,1.0,IF(T23=T26,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA23" s="14">
@@ -3692,27 +3692,27 @@
         <v/>
       </c>
       <c r="U24" s="14">
-        <f>IF(ISNUMBER(S24),IF(ISNUMBER(S23),IF(S24&gt;S23,1.0,IF(S24=S23,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S24),IF(ISNUMBER(S23),IF(S24&gt;S23,1.0,IF(S24=S23,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V24">
-        <f>IF(ISNUMBER(S24),IF(ISNUMBER(S25),IF(S24&gt;S25,1.0,IF(S24=S25,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S24),IF(ISNUMBER(S25),IF(S24&gt;S25,1.0,IF(S24=S25,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W24">
-        <f>IF(ISNUMBER(S24),IF(ISNUMBER(S26),IF(S24&gt;S26,1.0,IF(S24=S26,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S24),IF(ISNUMBER(S26),IF(S24&gt;S26,1.0,IF(S24=S26,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X24">
-        <f>IF(ISNUMBER(T24),IF(ISNUMBER(T23),IF(T24&gt;T23,1.0,IF(T24=T23,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T24),IF(ISNUMBER(T23),IF(T24&gt;T23,1.0,IF(T24=T23,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>IF(ISNUMBER(T24),IF(ISNUMBER(T25),IF(T24&gt;T25,1.0,IF(T24=T25,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T24),IF(ISNUMBER(T25),IF(T24&gt;T25,1.0,IF(T24=T25,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z24">
-        <f>IF(ISNUMBER(T24),IF(ISNUMBER(T26),IF(T24&gt;T26,1.0,IF(T24=T26,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T24),IF(ISNUMBER(T26),IF(T24&gt;T26,1.0,IF(T24=T26,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA24" s="14">
@@ -3818,27 +3818,27 @@
         <v/>
       </c>
       <c r="U25" s="14">
-        <f>IF(ISNUMBER(S25),IF(ISNUMBER(S23),IF(S25&gt;S23,1.0,IF(S25=S23,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S25),IF(ISNUMBER(S23),IF(S25&gt;S23,1.0,IF(S25=S23,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V25">
-        <f>IF(ISNUMBER(S25),IF(ISNUMBER(S24),IF(S25&gt;S24,1.0,IF(S25=S24,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S25),IF(ISNUMBER(S24),IF(S25&gt;S24,1.0,IF(S25=S24,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W25">
-        <f>IF(ISNUMBER(S25),IF(ISNUMBER(S26),IF(S25&gt;S26,1.0,IF(S25=S26,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S25),IF(ISNUMBER(S26),IF(S25&gt;S26,1.0,IF(S25=S26,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X25">
-        <f>IF(ISNUMBER(T25),IF(ISNUMBER(T23),IF(T25&gt;T23,1.0,IF(T25=T23,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T25),IF(ISNUMBER(T23),IF(T25&gt;T23,1.0,IF(T25=T23,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>IF(ISNUMBER(T25),IF(ISNUMBER(T24),IF(T25&gt;T24,1.0,IF(T25=T24,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T25),IF(ISNUMBER(T24),IF(T25&gt;T24,1.0,IF(T25=T24,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z25">
-        <f>IF(ISNUMBER(T25),IF(ISNUMBER(T26),IF(T25&gt;T26,1.0,IF(T25=T26,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T25),IF(ISNUMBER(T26),IF(T25&gt;T26,1.0,IF(T25=T26,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA25" s="14">
@@ -3945,27 +3945,27 @@
         <v/>
       </c>
       <c r="U26" s="21">
-        <f>IF(ISNUMBER(S26),IF(ISNUMBER(S23),IF(S26&gt;S23,1.0,IF(S26=S23,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S26),IF(ISNUMBER(S23),IF(S26&gt;S23,1.0,IF(S26=S23,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V26" s="15">
-        <f>IF(ISNUMBER(S26),IF(ISNUMBER(S24),IF(S26&gt;S24,1.0,IF(S26=S24,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S26),IF(ISNUMBER(S24),IF(S26&gt;S24,1.0,IF(S26=S24,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W26" s="15">
-        <f>IF(ISNUMBER(S26),IF(ISNUMBER(S25),IF(S26&gt;S25,1.0,IF(S26=S25,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S26),IF(ISNUMBER(S25),IF(S26&gt;S25,1.0,IF(S26=S25,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X26" s="15">
-        <f>IF(ISNUMBER(T26),IF(ISNUMBER(T23),IF(T26&gt;T23,1.0,IF(T26=T23,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T26),IF(ISNUMBER(T23),IF(T26&gt;T23,1.0,IF(T26=T23,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y26" s="15">
-        <f>IF(ISNUMBER(T26),IF(ISNUMBER(T24),IF(T26&gt;T24,1.0,IF(T26=T24,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T26),IF(ISNUMBER(T24),IF(T26&gt;T24,1.0,IF(T26=T24,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z26" s="15">
-        <f>IF(ISNUMBER(T26),IF(ISNUMBER(T25),IF(T26&gt;T25,1.0,IF(T26=T25,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T26),IF(ISNUMBER(T25),IF(T26&gt;T25,1.0,IF(T26=T25,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA26" s="21">
@@ -4074,27 +4074,27 @@
         <v/>
       </c>
       <c r="U27" s="14">
-        <f>IF(ISNUMBER(S27),IF(ISNUMBER(S28),IF(S27&gt;S28,1.0,IF(S27=S28,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S27),IF(ISNUMBER(S28),IF(S27&gt;S28,1.0,IF(S27=S28,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V27">
-        <f>IF(ISNUMBER(S27),IF(ISNUMBER(S29),IF(S27&gt;S29,1.0,IF(S27=S29,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S27),IF(ISNUMBER(S29),IF(S27&gt;S29,1.0,IF(S27=S29,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W27">
-        <f>IF(ISNUMBER(S27),IF(ISNUMBER(S30),IF(S27&gt;S30,1.0,IF(S27=S30,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S27),IF(ISNUMBER(S30),IF(S27&gt;S30,1.0,IF(S27=S30,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X27">
-        <f>IF(ISNUMBER(T27),IF(ISNUMBER(T28),IF(T27&gt;T28,1.0,IF(T27=T28,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T27),IF(ISNUMBER(T28),IF(T27&gt;T28,1.0,IF(T27=T28,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>IF(ISNUMBER(T27),IF(ISNUMBER(T29),IF(T27&gt;T29,1.0,IF(T27=T29,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T27),IF(ISNUMBER(T29),IF(T27&gt;T29,1.0,IF(T27=T29,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z27">
-        <f>IF(ISNUMBER(T27),IF(ISNUMBER(T30),IF(T27&gt;T30,1.0,IF(T27=T30,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T27),IF(ISNUMBER(T30),IF(T27&gt;T30,1.0,IF(T27=T30,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA27" s="14">
@@ -4200,27 +4200,27 @@
         <v/>
       </c>
       <c r="U28" s="14">
-        <f>IF(ISNUMBER(S28),IF(ISNUMBER(S27),IF(S28&gt;S27,1.0,IF(S28=S27,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S28),IF(ISNUMBER(S27),IF(S28&gt;S27,1.0,IF(S28=S27,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V28">
-        <f>IF(ISNUMBER(S28),IF(ISNUMBER(S29),IF(S28&gt;S29,1.0,IF(S28=S29,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S28),IF(ISNUMBER(S29),IF(S28&gt;S29,1.0,IF(S28=S29,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W28">
-        <f>IF(ISNUMBER(S28),IF(ISNUMBER(S30),IF(S28&gt;S30,1.0,IF(S28=S30,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S28),IF(ISNUMBER(S30),IF(S28&gt;S30,1.0,IF(S28=S30,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X28">
-        <f>IF(ISNUMBER(T28),IF(ISNUMBER(T27),IF(T28&gt;T27,1.0,IF(T28=T27,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T28),IF(ISNUMBER(T27),IF(T28&gt;T27,1.0,IF(T28=T27,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>IF(ISNUMBER(T28),IF(ISNUMBER(T29),IF(T28&gt;T29,1.0,IF(T28=T29,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T28),IF(ISNUMBER(T29),IF(T28&gt;T29,1.0,IF(T28=T29,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z28">
-        <f>IF(ISNUMBER(T28),IF(ISNUMBER(T30),IF(T28&gt;T30,1.0,IF(T28=T30,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T28),IF(ISNUMBER(T30),IF(T28&gt;T30,1.0,IF(T28=T30,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA28" s="14">
@@ -4326,27 +4326,27 @@
         <v/>
       </c>
       <c r="U29" s="14">
-        <f>IF(ISNUMBER(S29),IF(ISNUMBER(S27),IF(S29&gt;S27,1.0,IF(S29=S27,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S29),IF(ISNUMBER(S27),IF(S29&gt;S27,1.0,IF(S29=S27,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V29">
-        <f>IF(ISNUMBER(S29),IF(ISNUMBER(S28),IF(S29&gt;S28,1.0,IF(S29=S28,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S29),IF(ISNUMBER(S28),IF(S29&gt;S28,1.0,IF(S29=S28,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W29">
-        <f>IF(ISNUMBER(S29),IF(ISNUMBER(S30),IF(S29&gt;S30,1.0,IF(S29=S30,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S29),IF(ISNUMBER(S30),IF(S29&gt;S30,1.0,IF(S29=S30,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X29">
-        <f>IF(ISNUMBER(T29),IF(ISNUMBER(T27),IF(T29&gt;T27,1.0,IF(T29=T27,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T29),IF(ISNUMBER(T27),IF(T29&gt;T27,1.0,IF(T29=T27,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>IF(ISNUMBER(T29),IF(ISNUMBER(T28),IF(T29&gt;T28,1.0,IF(T29=T28,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T29),IF(ISNUMBER(T28),IF(T29&gt;T28,1.0,IF(T29=T28,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z29">
-        <f>IF(ISNUMBER(T29),IF(ISNUMBER(T30),IF(T29&gt;T30,1.0,IF(T29=T30,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T29),IF(ISNUMBER(T30),IF(T29&gt;T30,1.0,IF(T29=T30,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA29" s="14">
@@ -4453,27 +4453,27 @@
         <v/>
       </c>
       <c r="U30" s="21">
-        <f>IF(ISNUMBER(S30),IF(ISNUMBER(S27),IF(S30&gt;S27,1.0,IF(S30=S27,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S30),IF(ISNUMBER(S27),IF(S30&gt;S27,1.0,IF(S30=S27,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V30" s="15">
-        <f>IF(ISNUMBER(S30),IF(ISNUMBER(S28),IF(S30&gt;S28,1.0,IF(S30=S28,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S30),IF(ISNUMBER(S28),IF(S30&gt;S28,1.0,IF(S30=S28,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W30" s="15">
-        <f>IF(ISNUMBER(S30),IF(ISNUMBER(S29),IF(S30&gt;S29,1.0,IF(S30=S29,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S30),IF(ISNUMBER(S29),IF(S30&gt;S29,1.0,IF(S30=S29,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X30" s="15">
-        <f>IF(ISNUMBER(T30),IF(ISNUMBER(T27),IF(T30&gt;T27,1.0,IF(T30=T27,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T30),IF(ISNUMBER(T27),IF(T30&gt;T27,1.0,IF(T30=T27,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y30" s="15">
-        <f>IF(ISNUMBER(T30),IF(ISNUMBER(T28),IF(T30&gt;T28,1.0,IF(T30=T28,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T30),IF(ISNUMBER(T28),IF(T30&gt;T28,1.0,IF(T30=T28,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z30" s="15">
-        <f>IF(ISNUMBER(T30),IF(ISNUMBER(T29),IF(T30&gt;T29,1.0,IF(T30=T29,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T30),IF(ISNUMBER(T29),IF(T30&gt;T29,1.0,IF(T30=T29,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA30" s="21">
@@ -4582,27 +4582,27 @@
         <v/>
       </c>
       <c r="U31" s="14">
-        <f>IF(ISNUMBER(S31),IF(ISNUMBER(S32),IF(S31&gt;S32,1.0,IF(S31=S32,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S31),IF(ISNUMBER(S32),IF(S31&gt;S32,1.0,IF(S31=S32,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V31">
-        <f>IF(ISNUMBER(S31),IF(ISNUMBER(S33),IF(S31&gt;S33,1.0,IF(S31=S33,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S31),IF(ISNUMBER(S33),IF(S31&gt;S33,1.0,IF(S31=S33,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W31">
-        <f>IF(ISNUMBER(S31),IF(ISNUMBER(S34),IF(S31&gt;S34,1.0,IF(S31=S34,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S31),IF(ISNUMBER(S34),IF(S31&gt;S34,1.0,IF(S31=S34,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X31">
-        <f>IF(ISNUMBER(T31),IF(ISNUMBER(T32),IF(T31&gt;T32,1.0,IF(T31=T32,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T31),IF(ISNUMBER(T32),IF(T31&gt;T32,1.0,IF(T31=T32,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>IF(ISNUMBER(T31),IF(ISNUMBER(T33),IF(T31&gt;T33,1.0,IF(T31=T33,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T31),IF(ISNUMBER(T33),IF(T31&gt;T33,1.0,IF(T31=T33,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z31">
-        <f>IF(ISNUMBER(T31),IF(ISNUMBER(T34),IF(T31&gt;T34,1.0,IF(T31=T34,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T31),IF(ISNUMBER(T34),IF(T31&gt;T34,1.0,IF(T31=T34,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA31" s="14">
@@ -4708,27 +4708,27 @@
         <v/>
       </c>
       <c r="U32" s="14">
-        <f>IF(ISNUMBER(S32),IF(ISNUMBER(S31),IF(S32&gt;S31,1.0,IF(S32=S31,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S32),IF(ISNUMBER(S31),IF(S32&gt;S31,1.0,IF(S32=S31,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V32">
-        <f>IF(ISNUMBER(S32),IF(ISNUMBER(S33),IF(S32&gt;S33,1.0,IF(S32=S33,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S32),IF(ISNUMBER(S33),IF(S32&gt;S33,1.0,IF(S32=S33,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W32">
-        <f>IF(ISNUMBER(S32),IF(ISNUMBER(S34),IF(S32&gt;S34,1.0,IF(S32=S34,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S32),IF(ISNUMBER(S34),IF(S32&gt;S34,1.0,IF(S32=S34,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X32">
-        <f>IF(ISNUMBER(T32),IF(ISNUMBER(T31),IF(T32&gt;T31,1.0,IF(T32=T31,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T32),IF(ISNUMBER(T31),IF(T32&gt;T31,1.0,IF(T32=T31,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>IF(ISNUMBER(T32),IF(ISNUMBER(T33),IF(T32&gt;T33,1.0,IF(T32=T33,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T32),IF(ISNUMBER(T33),IF(T32&gt;T33,1.0,IF(T32=T33,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z32">
-        <f>IF(ISNUMBER(T32),IF(ISNUMBER(T34),IF(T32&gt;T34,1.0,IF(T32=T34,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T32),IF(ISNUMBER(T34),IF(T32&gt;T34,1.0,IF(T32=T34,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA32" s="14">
@@ -4834,27 +4834,27 @@
         <v/>
       </c>
       <c r="U33" s="14">
-        <f>IF(ISNUMBER(S33),IF(ISNUMBER(S31),IF(S33&gt;S31,1.0,IF(S33=S31,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S33),IF(ISNUMBER(S31),IF(S33&gt;S31,1.0,IF(S33=S31,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V33">
-        <f>IF(ISNUMBER(S33),IF(ISNUMBER(S32),IF(S33&gt;S32,1.0,IF(S33=S32,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S33),IF(ISNUMBER(S32),IF(S33&gt;S32,1.0,IF(S33=S32,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W33">
-        <f>IF(ISNUMBER(S33),IF(ISNUMBER(S34),IF(S33&gt;S34,1.0,IF(S33=S34,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S33),IF(ISNUMBER(S34),IF(S33&gt;S34,1.0,IF(S33=S34,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X33">
-        <f>IF(ISNUMBER(T33),IF(ISNUMBER(T31),IF(T33&gt;T31,1.0,IF(T33=T31,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T33),IF(ISNUMBER(T31),IF(T33&gt;T31,1.0,IF(T33=T31,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>IF(ISNUMBER(T33),IF(ISNUMBER(T32),IF(T33&gt;T32,1.0,IF(T33=T32,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T33),IF(ISNUMBER(T32),IF(T33&gt;T32,1.0,IF(T33=T32,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z33">
-        <f>IF(ISNUMBER(T33),IF(ISNUMBER(T34),IF(T33&gt;T34,1.0,IF(T33=T34,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T33),IF(ISNUMBER(T34),IF(T33&gt;T34,1.0,IF(T33=T34,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA33" s="14">
@@ -4961,27 +4961,27 @@
         <v/>
       </c>
       <c r="U34" s="21">
-        <f>IF(ISNUMBER(S34),IF(ISNUMBER(S31),IF(S34&gt;S31,1.0,IF(S34=S31,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S34),IF(ISNUMBER(S31),IF(S34&gt;S31,1.0,IF(S34=S31,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V34" s="15">
-        <f>IF(ISNUMBER(S34),IF(ISNUMBER(S32),IF(S34&gt;S32,1.0,IF(S34=S32,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S34),IF(ISNUMBER(S32),IF(S34&gt;S32,1.0,IF(S34=S32,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W34" s="15">
-        <f>IF(ISNUMBER(S34),IF(ISNUMBER(S33),IF(S34&gt;S33,1.0,IF(S34=S33,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S34),IF(ISNUMBER(S33),IF(S34&gt;S33,1.0,IF(S34=S33,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X34" s="15">
-        <f>IF(ISNUMBER(T34),IF(ISNUMBER(T31),IF(T34&gt;T31,1.0,IF(T34=T31,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T34),IF(ISNUMBER(T31),IF(T34&gt;T31,1.0,IF(T34=T31,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y34" s="15">
-        <f>IF(ISNUMBER(T34),IF(ISNUMBER(T32),IF(T34&gt;T32,1.0,IF(T34=T32,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T34),IF(ISNUMBER(T32),IF(T34&gt;T32,1.0,IF(T34=T32,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z34" s="15">
-        <f>IF(ISNUMBER(T34),IF(ISNUMBER(T33),IF(T34&gt;T33,1.0,IF(T34=T33,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T34),IF(ISNUMBER(T33),IF(T34&gt;T33,1.0,IF(T34=T33,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA34" s="21">
@@ -5090,27 +5090,27 @@
         <v/>
       </c>
       <c r="U35" s="14">
-        <f>IF(ISNUMBER(S35),IF(ISNUMBER(S36),IF(S35&gt;S36,1.0,IF(S35=S36,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S35),IF(ISNUMBER(S36),IF(S35&gt;S36,1.0,IF(S35=S36,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V35">
-        <f>IF(ISNUMBER(S35),IF(ISNUMBER(S37),IF(S35&gt;S37,1.0,IF(S35=S37,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S35),IF(ISNUMBER(S37),IF(S35&gt;S37,1.0,IF(S35=S37,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W35">
-        <f>IF(ISNUMBER(S35),IF(ISNUMBER(S38),IF(S35&gt;S38,1.0,IF(S35=S38,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S35),IF(ISNUMBER(S38),IF(S35&gt;S38,1.0,IF(S35=S38,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X35">
-        <f>IF(ISNUMBER(T35),IF(ISNUMBER(T36),IF(T35&gt;T36,1.0,IF(T35=T36,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T35),IF(ISNUMBER(T36),IF(T35&gt;T36,1.0,IF(T35=T36,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>IF(ISNUMBER(T35),IF(ISNUMBER(T37),IF(T35&gt;T37,1.0,IF(T35=T37,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T35),IF(ISNUMBER(T37),IF(T35&gt;T37,1.0,IF(T35=T37,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z35">
-        <f>IF(ISNUMBER(T35),IF(ISNUMBER(T38),IF(T35&gt;T38,1.0,IF(T35=T38,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T35),IF(ISNUMBER(T38),IF(T35&gt;T38,1.0,IF(T35=T38,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA35" s="14">
@@ -5216,27 +5216,27 @@
         <v/>
       </c>
       <c r="U36" s="14">
-        <f>IF(ISNUMBER(S36),IF(ISNUMBER(S35),IF(S36&gt;S35,1.0,IF(S36=S35,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S36),IF(ISNUMBER(S35),IF(S36&gt;S35,1.0,IF(S36=S35,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V36">
-        <f>IF(ISNUMBER(S36),IF(ISNUMBER(S37),IF(S36&gt;S37,1.0,IF(S36=S37,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S36),IF(ISNUMBER(S37),IF(S36&gt;S37,1.0,IF(S36=S37,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W36">
-        <f>IF(ISNUMBER(S36),IF(ISNUMBER(S38),IF(S36&gt;S38,1.0,IF(S36=S38,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S36),IF(ISNUMBER(S38),IF(S36&gt;S38,1.0,IF(S36=S38,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X36">
-        <f>IF(ISNUMBER(T36),IF(ISNUMBER(T35),IF(T36&gt;T35,1.0,IF(T36=T35,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T36),IF(ISNUMBER(T35),IF(T36&gt;T35,1.0,IF(T36=T35,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>IF(ISNUMBER(T36),IF(ISNUMBER(T37),IF(T36&gt;T37,1.0,IF(T36=T37,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T36),IF(ISNUMBER(T37),IF(T36&gt;T37,1.0,IF(T36=T37,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z36">
-        <f>IF(ISNUMBER(T36),IF(ISNUMBER(T38),IF(T36&gt;T38,1.0,IF(T36=T38,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T36),IF(ISNUMBER(T38),IF(T36&gt;T38,1.0,IF(T36=T38,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA36" s="14">
@@ -5342,27 +5342,27 @@
         <v/>
       </c>
       <c r="U37" s="14">
-        <f>IF(ISNUMBER(S37),IF(ISNUMBER(S35),IF(S37&gt;S35,1.0,IF(S37=S35,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S37),IF(ISNUMBER(S35),IF(S37&gt;S35,1.0,IF(S37=S35,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V37">
-        <f>IF(ISNUMBER(S37),IF(ISNUMBER(S36),IF(S37&gt;S36,1.0,IF(S37=S36,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S37),IF(ISNUMBER(S36),IF(S37&gt;S36,1.0,IF(S37=S36,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W37">
-        <f>IF(ISNUMBER(S37),IF(ISNUMBER(S38),IF(S37&gt;S38,1.0,IF(S37=S38,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S37),IF(ISNUMBER(S38),IF(S37&gt;S38,1.0,IF(S37=S38,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X37">
-        <f>IF(ISNUMBER(T37),IF(ISNUMBER(T35),IF(T37&gt;T35,1.0,IF(T37=T35,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T37),IF(ISNUMBER(T35),IF(T37&gt;T35,1.0,IF(T37=T35,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>IF(ISNUMBER(T37),IF(ISNUMBER(T36),IF(T37&gt;T36,1.0,IF(T37=T36,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T37),IF(ISNUMBER(T36),IF(T37&gt;T36,1.0,IF(T37=T36,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z37">
-        <f>IF(ISNUMBER(T37),IF(ISNUMBER(T38),IF(T37&gt;T38,1.0,IF(T37=T38,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T37),IF(ISNUMBER(T38),IF(T37&gt;T38,1.0,IF(T37=T38,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA37" s="14">
@@ -5469,27 +5469,27 @@
         <v/>
       </c>
       <c r="U38" s="21">
-        <f>IF(ISNUMBER(S38),IF(ISNUMBER(S35),IF(S38&gt;S35,1.0,IF(S38=S35,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S38),IF(ISNUMBER(S35),IF(S38&gt;S35,1.0,IF(S38=S35,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V38" s="15">
-        <f>IF(ISNUMBER(S38),IF(ISNUMBER(S36),IF(S38&gt;S36,1.0,IF(S38=S36,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S38),IF(ISNUMBER(S36),IF(S38&gt;S36,1.0,IF(S38=S36,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W38" s="15">
-        <f>IF(ISNUMBER(S38),IF(ISNUMBER(S37),IF(S38&gt;S37,1.0,IF(S38=S37,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S38),IF(ISNUMBER(S37),IF(S38&gt;S37,1.0,IF(S38=S37,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X38" s="15">
-        <f>IF(ISNUMBER(T38),IF(ISNUMBER(T35),IF(T38&gt;T35,1.0,IF(T38=T35,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T38),IF(ISNUMBER(T35),IF(T38&gt;T35,1.0,IF(T38=T35,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y38" s="15">
-        <f>IF(ISNUMBER(T38),IF(ISNUMBER(T36),IF(T38&gt;T36,1.0,IF(T38=T36,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T38),IF(ISNUMBER(T36),IF(T38&gt;T36,1.0,IF(T38=T36,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z38" s="15">
-        <f>IF(ISNUMBER(T38),IF(ISNUMBER(T37),IF(T38&gt;T37,1.0,IF(T38=T37,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T38),IF(ISNUMBER(T37),IF(T38&gt;T37,1.0,IF(T38=T37,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA38" s="21">
@@ -5598,27 +5598,27 @@
         <v/>
       </c>
       <c r="U39" s="14">
-        <f>IF(ISNUMBER(S39),IF(ISNUMBER(S40),IF(S39&gt;S40,1.0,IF(S39=S40,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S39),IF(ISNUMBER(S40),IF(S39&gt;S40,1.0,IF(S39=S40,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V39">
-        <f>IF(ISNUMBER(S39),IF(ISNUMBER(S41),IF(S39&gt;S41,1.0,IF(S39=S41,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S39),IF(ISNUMBER(S41),IF(S39&gt;S41,1.0,IF(S39=S41,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W39">
-        <f>IF(ISNUMBER(S39),IF(ISNUMBER(S42),IF(S39&gt;S42,1.0,IF(S39=S42,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S39),IF(ISNUMBER(S42),IF(S39&gt;S42,1.0,IF(S39=S42,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X39">
-        <f>IF(ISNUMBER(T39),IF(ISNUMBER(T40),IF(T39&gt;T40,1.0,IF(T39=T40,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T39),IF(ISNUMBER(T40),IF(T39&gt;T40,1.0,IF(T39=T40,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>IF(ISNUMBER(T39),IF(ISNUMBER(T41),IF(T39&gt;T41,1.0,IF(T39=T41,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T39),IF(ISNUMBER(T41),IF(T39&gt;T41,1.0,IF(T39=T41,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z39">
-        <f>IF(ISNUMBER(T39),IF(ISNUMBER(T42),IF(T39&gt;T42,1.0,IF(T39=T42,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T39),IF(ISNUMBER(T42),IF(T39&gt;T42,1.0,IF(T39=T42,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA39" s="14">
@@ -5724,27 +5724,27 @@
         <v/>
       </c>
       <c r="U40" s="14">
-        <f>IF(ISNUMBER(S40),IF(ISNUMBER(S39),IF(S40&gt;S39,1.0,IF(S40=S39,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S40),IF(ISNUMBER(S39),IF(S40&gt;S39,1.0,IF(S40=S39,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V40">
-        <f>IF(ISNUMBER(S40),IF(ISNUMBER(S41),IF(S40&gt;S41,1.0,IF(S40=S41,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S40),IF(ISNUMBER(S41),IF(S40&gt;S41,1.0,IF(S40=S41,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W40">
-        <f>IF(ISNUMBER(S40),IF(ISNUMBER(S42),IF(S40&gt;S42,1.0,IF(S40=S42,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S40),IF(ISNUMBER(S42),IF(S40&gt;S42,1.0,IF(S40=S42,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X40">
-        <f>IF(ISNUMBER(T40),IF(ISNUMBER(T39),IF(T40&gt;T39,1.0,IF(T40=T39,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T40),IF(ISNUMBER(T39),IF(T40&gt;T39,1.0,IF(T40=T39,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>IF(ISNUMBER(T40),IF(ISNUMBER(T41),IF(T40&gt;T41,1.0,IF(T40=T41,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T40),IF(ISNUMBER(T41),IF(T40&gt;T41,1.0,IF(T40=T41,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z40">
-        <f>IF(ISNUMBER(T40),IF(ISNUMBER(T42),IF(T40&gt;T42,1.0,IF(T40=T42,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T40),IF(ISNUMBER(T42),IF(T40&gt;T42,1.0,IF(T40=T42,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA40" s="14">
@@ -5850,27 +5850,27 @@
         <v/>
       </c>
       <c r="U41" s="14">
-        <f>IF(ISNUMBER(S41),IF(ISNUMBER(S39),IF(S41&gt;S39,1.0,IF(S41=S39,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S41),IF(ISNUMBER(S39),IF(S41&gt;S39,1.0,IF(S41=S39,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V41">
-        <f>IF(ISNUMBER(S41),IF(ISNUMBER(S40),IF(S41&gt;S40,1.0,IF(S41=S40,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S41),IF(ISNUMBER(S40),IF(S41&gt;S40,1.0,IF(S41=S40,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W41">
-        <f>IF(ISNUMBER(S41),IF(ISNUMBER(S42),IF(S41&gt;S42,1.0,IF(S41=S42,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S41),IF(ISNUMBER(S42),IF(S41&gt;S42,1.0,IF(S41=S42,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X41">
-        <f>IF(ISNUMBER(T41),IF(ISNUMBER(T39),IF(T41&gt;T39,1.0,IF(T41=T39,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T41),IF(ISNUMBER(T39),IF(T41&gt;T39,1.0,IF(T41=T39,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>IF(ISNUMBER(T41),IF(ISNUMBER(T40),IF(T41&gt;T40,1.0,IF(T41=T40,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T41),IF(ISNUMBER(T40),IF(T41&gt;T40,1.0,IF(T41=T40,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z41">
-        <f>IF(ISNUMBER(T41),IF(ISNUMBER(T42),IF(T41&gt;T42,1.0,IF(T41=T42,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T41),IF(ISNUMBER(T42),IF(T41&gt;T42,1.0,IF(T41=T42,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA41" s="14">
@@ -5977,27 +5977,27 @@
         <v/>
       </c>
       <c r="U42" s="21">
-        <f>IF(ISNUMBER(S42),IF(ISNUMBER(S39),IF(S42&gt;S39,1.0,IF(S42=S39,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S42),IF(ISNUMBER(S39),IF(S42&gt;S39,1.0,IF(S42=S39,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V42" s="15">
-        <f>IF(ISNUMBER(S42),IF(ISNUMBER(S40),IF(S42&gt;S40,1.0,IF(S42=S40,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S42),IF(ISNUMBER(S40),IF(S42&gt;S40,1.0,IF(S42=S40,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W42" s="15">
-        <f>IF(ISNUMBER(S42),IF(ISNUMBER(S41),IF(S42&gt;S41,1.0,IF(S42=S41,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S42),IF(ISNUMBER(S41),IF(S42&gt;S41,1.0,IF(S42=S41,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X42" s="15">
-        <f>IF(ISNUMBER(T42),IF(ISNUMBER(T39),IF(T42&gt;T39,1.0,IF(T42=T39,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T42),IF(ISNUMBER(T39),IF(T42&gt;T39,1.0,IF(T42=T39,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y42" s="15">
-        <f>IF(ISNUMBER(T42),IF(ISNUMBER(T40),IF(T42&gt;T40,1.0,IF(T42=T40,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T42),IF(ISNUMBER(T40),IF(T42&gt;T40,1.0,IF(T42=T40,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z42" s="15">
-        <f>IF(ISNUMBER(T42),IF(ISNUMBER(T41),IF(T42&gt;T41,1.0,IF(T42=T41,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T42),IF(ISNUMBER(T41),IF(T42&gt;T41,1.0,IF(T42=T41,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA42" s="21">
@@ -6106,27 +6106,27 @@
         <v/>
       </c>
       <c r="U43" s="14">
-        <f>IF(ISNUMBER(S43),IF(ISNUMBER(S44),IF(S43&gt;S44,1.0,IF(S43=S44,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S43),IF(ISNUMBER(S44),IF(S43&gt;S44,1.0,IF(S43=S44,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V43">
-        <f>IF(ISNUMBER(S43),IF(ISNUMBER(S45),IF(S43&gt;S45,1.0,IF(S43=S45,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S43),IF(ISNUMBER(S45),IF(S43&gt;S45,1.0,IF(S43=S45,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W43">
-        <f>IF(ISNUMBER(S43),IF(ISNUMBER(S46),IF(S43&gt;S46,1.0,IF(S43=S46,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S43),IF(ISNUMBER(S46),IF(S43&gt;S46,1.0,IF(S43=S46,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X43">
-        <f>IF(ISNUMBER(T43),IF(ISNUMBER(T44),IF(T43&gt;T44,1.0,IF(T43=T44,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T43),IF(ISNUMBER(T44),IF(T43&gt;T44,1.0,IF(T43=T44,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>IF(ISNUMBER(T43),IF(ISNUMBER(T45),IF(T43&gt;T45,1.0,IF(T43=T45,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T43),IF(ISNUMBER(T45),IF(T43&gt;T45,1.0,IF(T43=T45,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z43">
-        <f>IF(ISNUMBER(T43),IF(ISNUMBER(T46),IF(T43&gt;T46,1.0,IF(T43=T46,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T43),IF(ISNUMBER(T46),IF(T43&gt;T46,1.0,IF(T43=T46,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA43" s="14">
@@ -6232,27 +6232,27 @@
         <v/>
       </c>
       <c r="U44" s="14">
-        <f>IF(ISNUMBER(S44),IF(ISNUMBER(S43),IF(S44&gt;S43,1.0,IF(S44=S43,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S44),IF(ISNUMBER(S43),IF(S44&gt;S43,1.0,IF(S44=S43,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V44">
-        <f>IF(ISNUMBER(S44),IF(ISNUMBER(S45),IF(S44&gt;S45,1.0,IF(S44=S45,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S44),IF(ISNUMBER(S45),IF(S44&gt;S45,1.0,IF(S44=S45,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W44">
-        <f>IF(ISNUMBER(S44),IF(ISNUMBER(S46),IF(S44&gt;S46,1.0,IF(S44=S46,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S44),IF(ISNUMBER(S46),IF(S44&gt;S46,1.0,IF(S44=S46,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X44">
-        <f>IF(ISNUMBER(T44),IF(ISNUMBER(T43),IF(T44&gt;T43,1.0,IF(T44=T43,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T44),IF(ISNUMBER(T43),IF(T44&gt;T43,1.0,IF(T44=T43,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>IF(ISNUMBER(T44),IF(ISNUMBER(T45),IF(T44&gt;T45,1.0,IF(T44=T45,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T44),IF(ISNUMBER(T45),IF(T44&gt;T45,1.0,IF(T44=T45,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z44">
-        <f>IF(ISNUMBER(T44),IF(ISNUMBER(T46),IF(T44&gt;T46,1.0,IF(T44=T46,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T44),IF(ISNUMBER(T46),IF(T44&gt;T46,1.0,IF(T44=T46,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA44" s="14">
@@ -6358,27 +6358,27 @@
         <v/>
       </c>
       <c r="U45" s="14">
-        <f>IF(ISNUMBER(S45),IF(ISNUMBER(S43),IF(S45&gt;S43,1.0,IF(S45=S43,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S45),IF(ISNUMBER(S43),IF(S45&gt;S43,1.0,IF(S45=S43,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V45">
-        <f>IF(ISNUMBER(S45),IF(ISNUMBER(S44),IF(S45&gt;S44,1.0,IF(S45=S44,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S45),IF(ISNUMBER(S44),IF(S45&gt;S44,1.0,IF(S45=S44,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W45">
-        <f>IF(ISNUMBER(S45),IF(ISNUMBER(S46),IF(S45&gt;S46,1.0,IF(S45=S46,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S45),IF(ISNUMBER(S46),IF(S45&gt;S46,1.0,IF(S45=S46,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X45">
-        <f>IF(ISNUMBER(T45),IF(ISNUMBER(T43),IF(T45&gt;T43,1.0,IF(T45=T43,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T45),IF(ISNUMBER(T43),IF(T45&gt;T43,1.0,IF(T45=T43,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>IF(ISNUMBER(T45),IF(ISNUMBER(T44),IF(T45&gt;T44,1.0,IF(T45=T44,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T45),IF(ISNUMBER(T44),IF(T45&gt;T44,1.0,IF(T45=T44,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z45">
-        <f>IF(ISNUMBER(T45),IF(ISNUMBER(T46),IF(T45&gt;T46,1.0,IF(T45=T46,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T45),IF(ISNUMBER(T46),IF(T45&gt;T46,1.0,IF(T45=T46,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA45" s="14">
@@ -6485,27 +6485,27 @@
         <v/>
       </c>
       <c r="U46" s="21">
-        <f>IF(ISNUMBER(S46),IF(ISNUMBER(S43),IF(S46&gt;S43,1.0,IF(S46=S43,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S46),IF(ISNUMBER(S43),IF(S46&gt;S43,1.0,IF(S46=S43,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V46" s="15">
-        <f>IF(ISNUMBER(S46),IF(ISNUMBER(S44),IF(S46&gt;S44,1.0,IF(S46=S44,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S46),IF(ISNUMBER(S44),IF(S46&gt;S44,1.0,IF(S46=S44,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W46" s="15">
-        <f>IF(ISNUMBER(S46),IF(ISNUMBER(S45),IF(S46&gt;S45,1.0,IF(S46=S45,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S46),IF(ISNUMBER(S45),IF(S46&gt;S45,1.0,IF(S46=S45,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X46" s="15">
-        <f>IF(ISNUMBER(T46),IF(ISNUMBER(T43),IF(T46&gt;T43,1.0,IF(T46=T43,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T46),IF(ISNUMBER(T43),IF(T46&gt;T43,1.0,IF(T46=T43,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y46" s="15">
-        <f>IF(ISNUMBER(T46),IF(ISNUMBER(T44),IF(T46&gt;T44,1.0,IF(T46=T44,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T46),IF(ISNUMBER(T44),IF(T46&gt;T44,1.0,IF(T46=T44,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z46" s="15">
-        <f>IF(ISNUMBER(T46),IF(ISNUMBER(T45),IF(T46&gt;T45,1.0,IF(T46=T45,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T46),IF(ISNUMBER(T45),IF(T46&gt;T45,1.0,IF(T46=T45,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA46" s="21">
@@ -6614,27 +6614,27 @@
         <v/>
       </c>
       <c r="U47" s="14">
-        <f>IF(ISNUMBER(S47),IF(ISNUMBER(S48),IF(S47&gt;S48,1.0,IF(S47=S48,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S47),IF(ISNUMBER(S48),IF(S47&gt;S48,1.0,IF(S47=S48,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V47">
-        <f>IF(ISNUMBER(S47),IF(ISNUMBER(S49),IF(S47&gt;S49,1.0,IF(S47=S49,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S47),IF(ISNUMBER(S49),IF(S47&gt;S49,1.0,IF(S47=S49,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W47">
-        <f>IF(ISNUMBER(S47),IF(ISNUMBER(S50),IF(S47&gt;S50,1.0,IF(S47=S50,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S47),IF(ISNUMBER(S50),IF(S47&gt;S50,1.0,IF(S47=S50,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X47">
-        <f>IF(ISNUMBER(T47),IF(ISNUMBER(T48),IF(T47&gt;T48,1.0,IF(T47=T48,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T47),IF(ISNUMBER(T48),IF(T47&gt;T48,1.0,IF(T47=T48,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>IF(ISNUMBER(T47),IF(ISNUMBER(T49),IF(T47&gt;T49,1.0,IF(T47=T49,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T47),IF(ISNUMBER(T49),IF(T47&gt;T49,1.0,IF(T47=T49,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z47">
-        <f>IF(ISNUMBER(T47),IF(ISNUMBER(T50),IF(T47&gt;T50,1.0,IF(T47=T50,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T47),IF(ISNUMBER(T50),IF(T47&gt;T50,1.0,IF(T47=T50,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA47" s="14">
@@ -6740,27 +6740,27 @@
         <v/>
       </c>
       <c r="U48" s="14">
-        <f>IF(ISNUMBER(S48),IF(ISNUMBER(S47),IF(S48&gt;S47,1.0,IF(S48=S47,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S48),IF(ISNUMBER(S47),IF(S48&gt;S47,1.0,IF(S48=S47,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V48">
-        <f>IF(ISNUMBER(S48),IF(ISNUMBER(S49),IF(S48&gt;S49,1.0,IF(S48=S49,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S48),IF(ISNUMBER(S49),IF(S48&gt;S49,1.0,IF(S48=S49,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W48">
-        <f>IF(ISNUMBER(S48),IF(ISNUMBER(S50),IF(S48&gt;S50,1.0,IF(S48=S50,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S48),IF(ISNUMBER(S50),IF(S48&gt;S50,1.0,IF(S48=S50,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X48">
-        <f>IF(ISNUMBER(T48),IF(ISNUMBER(T47),IF(T48&gt;T47,1.0,IF(T48=T47,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T48),IF(ISNUMBER(T47),IF(T48&gt;T47,1.0,IF(T48=T47,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y48">
-        <f>IF(ISNUMBER(T48),IF(ISNUMBER(T49),IF(T48&gt;T49,1.0,IF(T48=T49,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T48),IF(ISNUMBER(T49),IF(T48&gt;T49,1.0,IF(T48=T49,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z48">
-        <f>IF(ISNUMBER(T48),IF(ISNUMBER(T50),IF(T48&gt;T50,1.0,IF(T48=T50,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T48),IF(ISNUMBER(T50),IF(T48&gt;T50,1.0,IF(T48=T50,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA48" s="14">
@@ -6866,27 +6866,27 @@
         <v/>
       </c>
       <c r="U49" s="14">
-        <f>IF(ISNUMBER(S49),IF(ISNUMBER(S47),IF(S49&gt;S47,1.0,IF(S49=S47,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S49),IF(ISNUMBER(S47),IF(S49&gt;S47,1.0,IF(S49=S47,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V49">
-        <f>IF(ISNUMBER(S49),IF(ISNUMBER(S48),IF(S49&gt;S48,1.0,IF(S49=S48,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S49),IF(ISNUMBER(S48),IF(S49&gt;S48,1.0,IF(S49=S48,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W49">
-        <f>IF(ISNUMBER(S49),IF(ISNUMBER(S50),IF(S49&gt;S50,1.0,IF(S49=S50,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S49),IF(ISNUMBER(S50),IF(S49&gt;S50,1.0,IF(S49=S50,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X49">
-        <f>IF(ISNUMBER(T49),IF(ISNUMBER(T47),IF(T49&gt;T47,1.0,IF(T49=T47,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T49),IF(ISNUMBER(T47),IF(T49&gt;T47,1.0,IF(T49=T47,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y49">
-        <f>IF(ISNUMBER(T49),IF(ISNUMBER(T48),IF(T49&gt;T48,1.0,IF(T49=T48,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T49),IF(ISNUMBER(T48),IF(T49&gt;T48,1.0,IF(T49=T48,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z49">
-        <f>IF(ISNUMBER(T49),IF(ISNUMBER(T50),IF(T49&gt;T50,1.0,IF(T49=T50,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T49),IF(ISNUMBER(T50),IF(T49&gt;T50,1.0,IF(T49=T50,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA49" s="14">
@@ -6993,27 +6993,27 @@
         <v/>
       </c>
       <c r="U50" s="21">
-        <f>IF(ISNUMBER(S50),IF(ISNUMBER(S47),IF(S50&gt;S47,1.0,IF(S50=S47,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S50),IF(ISNUMBER(S47),IF(S50&gt;S47,1.0,IF(S50=S47,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V50" s="15">
-        <f>IF(ISNUMBER(S50),IF(ISNUMBER(S48),IF(S50&gt;S48,1.0,IF(S50=S48,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S50),IF(ISNUMBER(S48),IF(S50&gt;S48,1.0,IF(S50=S48,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W50" s="15">
-        <f>IF(ISNUMBER(S50),IF(ISNUMBER(S49),IF(S50&gt;S49,1.0,IF(S50=S49,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S50),IF(ISNUMBER(S49),IF(S50&gt;S49,1.0,IF(S50=S49,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X50" s="15">
-        <f>IF(ISNUMBER(T50),IF(ISNUMBER(T47),IF(T50&gt;T47,1.0,IF(T50=T47,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T50),IF(ISNUMBER(T47),IF(T50&gt;T47,1.0,IF(T50=T47,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y50" s="15">
-        <f>IF(ISNUMBER(T50),IF(ISNUMBER(T48),IF(T50&gt;T48,1.0,IF(T50=T48,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T50),IF(ISNUMBER(T48),IF(T50&gt;T48,1.0,IF(T50=T48,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z50" s="15">
-        <f>IF(ISNUMBER(T50),IF(ISNUMBER(T49),IF(T50&gt;T49,1.0,IF(T50=T49,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T50),IF(ISNUMBER(T49),IF(T50&gt;T49,1.0,IF(T50=T49,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA50" s="21">
@@ -7122,27 +7122,27 @@
         <v/>
       </c>
       <c r="U51" s="14">
-        <f>IF(ISNUMBER(S51),IF(ISNUMBER(S52),IF(S51&gt;S52,1.0,IF(S51=S52,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S51),IF(ISNUMBER(S52),IF(S51&gt;S52,1.0,IF(S51=S52,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V51">
-        <f>IF(ISNUMBER(S51),IF(ISNUMBER(S53),IF(S51&gt;S53,1.0,IF(S51=S53,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S51),IF(ISNUMBER(S53),IF(S51&gt;S53,1.0,IF(S51=S53,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W51">
-        <f>IF(ISNUMBER(S51),IF(ISNUMBER(S54),IF(S51&gt;S54,1.0,IF(S51=S54,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S51),IF(ISNUMBER(S54),IF(S51&gt;S54,1.0,IF(S51=S54,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X51">
-        <f>IF(ISNUMBER(T51),IF(ISNUMBER(T52),IF(T51&gt;T52,1.0,IF(T51=T52,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T51),IF(ISNUMBER(T52),IF(T51&gt;T52,1.0,IF(T51=T52,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y51">
-        <f>IF(ISNUMBER(T51),IF(ISNUMBER(T53),IF(T51&gt;T53,1.0,IF(T51=T53,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T51),IF(ISNUMBER(T53),IF(T51&gt;T53,1.0,IF(T51=T53,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z51">
-        <f>IF(ISNUMBER(T51),IF(ISNUMBER(T54),IF(T51&gt;T54,1.0,IF(T51=T54,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T51),IF(ISNUMBER(T54),IF(T51&gt;T54,1.0,IF(T51=T54,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA51" s="14">
@@ -7248,27 +7248,27 @@
         <v/>
       </c>
       <c r="U52" s="14">
-        <f>IF(ISNUMBER(S52),IF(ISNUMBER(S51),IF(S52&gt;S51,1.0,IF(S52=S51,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S52),IF(ISNUMBER(S51),IF(S52&gt;S51,1.0,IF(S52=S51,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V52">
-        <f>IF(ISNUMBER(S52),IF(ISNUMBER(S53),IF(S52&gt;S53,1.0,IF(S52=S53,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S52),IF(ISNUMBER(S53),IF(S52&gt;S53,1.0,IF(S52=S53,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W52">
-        <f>IF(ISNUMBER(S52),IF(ISNUMBER(S54),IF(S52&gt;S54,1.0,IF(S52=S54,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S52),IF(ISNUMBER(S54),IF(S52&gt;S54,1.0,IF(S52=S54,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X52">
-        <f>IF(ISNUMBER(T52),IF(ISNUMBER(T51),IF(T52&gt;T51,1.0,IF(T52=T51,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T52),IF(ISNUMBER(T51),IF(T52&gt;T51,1.0,IF(T52=T51,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y52">
-        <f>IF(ISNUMBER(T52),IF(ISNUMBER(T53),IF(T52&gt;T53,1.0,IF(T52=T53,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T52),IF(ISNUMBER(T53),IF(T52&gt;T53,1.0,IF(T52=T53,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z52">
-        <f>IF(ISNUMBER(T52),IF(ISNUMBER(T54),IF(T52&gt;T54,1.0,IF(T52=T54,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T52),IF(ISNUMBER(T54),IF(T52&gt;T54,1.0,IF(T52=T54,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA52" s="14">
@@ -7374,27 +7374,27 @@
         <v/>
       </c>
       <c r="U53" s="14">
-        <f>IF(ISNUMBER(S53),IF(ISNUMBER(S51),IF(S53&gt;S51,1.0,IF(S53=S51,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S53),IF(ISNUMBER(S51),IF(S53&gt;S51,1.0,IF(S53=S51,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V53">
-        <f>IF(ISNUMBER(S53),IF(ISNUMBER(S52),IF(S53&gt;S52,1.0,IF(S53=S52,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S53),IF(ISNUMBER(S52),IF(S53&gt;S52,1.0,IF(S53=S52,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W53">
-        <f>IF(ISNUMBER(S53),IF(ISNUMBER(S54),IF(S53&gt;S54,1.0,IF(S53=S54,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S53),IF(ISNUMBER(S54),IF(S53&gt;S54,1.0,IF(S53=S54,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X53">
-        <f>IF(ISNUMBER(T53),IF(ISNUMBER(T51),IF(T53&gt;T51,1.0,IF(T53=T51,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T53),IF(ISNUMBER(T51),IF(T53&gt;T51,1.0,IF(T53=T51,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y53">
-        <f>IF(ISNUMBER(T53),IF(ISNUMBER(T52),IF(T53&gt;T52,1.0,IF(T53=T52,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T53),IF(ISNUMBER(T52),IF(T53&gt;T52,1.0,IF(T53=T52,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z53">
-        <f>IF(ISNUMBER(T53),IF(ISNUMBER(T54),IF(T53&gt;T54,1.0,IF(T53=T54,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T53),IF(ISNUMBER(T54),IF(T53&gt;T54,1.0,IF(T53=T54,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA53" s="14">
@@ -7501,27 +7501,27 @@
         <v/>
       </c>
       <c r="U54" s="21">
-        <f>IF(ISNUMBER(S54),IF(ISNUMBER(S51),IF(S54&gt;S51,1.0,IF(S54=S51,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S54),IF(ISNUMBER(S51),IF(S54&gt;S51,1.0,IF(S54=S51,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V54" s="15">
-        <f>IF(ISNUMBER(S54),IF(ISNUMBER(S52),IF(S54&gt;S52,1.0,IF(S54=S52,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S54),IF(ISNUMBER(S52),IF(S54&gt;S52,1.0,IF(S54=S52,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W54" s="15">
-        <f>IF(ISNUMBER(S54),IF(ISNUMBER(S53),IF(S54&gt;S53,1.0,IF(S54=S53,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S54),IF(ISNUMBER(S53),IF(S54&gt;S53,1.0,IF(S54=S53,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X54" s="15">
-        <f>IF(ISNUMBER(T54),IF(ISNUMBER(T51),IF(T54&gt;T51,1.0,IF(T54=T51,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T54),IF(ISNUMBER(T51),IF(T54&gt;T51,1.0,IF(T54=T51,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y54" s="15">
-        <f>IF(ISNUMBER(T54),IF(ISNUMBER(T52),IF(T54&gt;T52,1.0,IF(T54=T52,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T54),IF(ISNUMBER(T52),IF(T54&gt;T52,1.0,IF(T54=T52,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z54" s="15">
-        <f>IF(ISNUMBER(T54),IF(ISNUMBER(T53),IF(T54&gt;T53,1.0,IF(T54=T53,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T54),IF(ISNUMBER(T53),IF(T54&gt;T53,1.0,IF(T54=T53,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA54" s="21">
@@ -7630,27 +7630,27 @@
         <v/>
       </c>
       <c r="U55" s="14">
-        <f>IF(ISNUMBER(S55),IF(ISNUMBER(S56),IF(S55&gt;S56,1.0,IF(S55=S56,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S55),IF(ISNUMBER(S56),IF(S55&gt;S56,1.0,IF(S55=S56,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V55">
-        <f>IF(ISNUMBER(S55),IF(ISNUMBER(S57),IF(S55&gt;S57,1.0,IF(S55=S57,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S55),IF(ISNUMBER(S57),IF(S55&gt;S57,1.0,IF(S55=S57,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W55">
-        <f>IF(ISNUMBER(S55),IF(ISNUMBER(S58),IF(S55&gt;S58,1.0,IF(S55=S58,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S55),IF(ISNUMBER(S58),IF(S55&gt;S58,1.0,IF(S55=S58,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X55">
-        <f>IF(ISNUMBER(T55),IF(ISNUMBER(T56),IF(T55&gt;T56,1.0,IF(T55=T56,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T55),IF(ISNUMBER(T56),IF(T55&gt;T56,1.0,IF(T55=T56,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y55">
-        <f>IF(ISNUMBER(T55),IF(ISNUMBER(T57),IF(T55&gt;T57,1.0,IF(T55=T57,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T55),IF(ISNUMBER(T57),IF(T55&gt;T57,1.0,IF(T55=T57,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z55">
-        <f>IF(ISNUMBER(T55),IF(ISNUMBER(T58),IF(T55&gt;T58,1.0,IF(T55=T58,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T55),IF(ISNUMBER(T58),IF(T55&gt;T58,1.0,IF(T55=T58,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA55" s="14">
@@ -7756,27 +7756,27 @@
         <v/>
       </c>
       <c r="U56" s="14">
-        <f>IF(ISNUMBER(S56),IF(ISNUMBER(S55),IF(S56&gt;S55,1.0,IF(S56=S55,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S56),IF(ISNUMBER(S55),IF(S56&gt;S55,1.0,IF(S56=S55,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V56">
-        <f>IF(ISNUMBER(S56),IF(ISNUMBER(S57),IF(S56&gt;S57,1.0,IF(S56=S57,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S56),IF(ISNUMBER(S57),IF(S56&gt;S57,1.0,IF(S56=S57,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W56">
-        <f>IF(ISNUMBER(S56),IF(ISNUMBER(S58),IF(S56&gt;S58,1.0,IF(S56=S58,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S56),IF(ISNUMBER(S58),IF(S56&gt;S58,1.0,IF(S56=S58,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X56">
-        <f>IF(ISNUMBER(T56),IF(ISNUMBER(T55),IF(T56&gt;T55,1.0,IF(T56=T55,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T56),IF(ISNUMBER(T55),IF(T56&gt;T55,1.0,IF(T56=T55,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y56">
-        <f>IF(ISNUMBER(T56),IF(ISNUMBER(T57),IF(T56&gt;T57,1.0,IF(T56=T57,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T56),IF(ISNUMBER(T57),IF(T56&gt;T57,1.0,IF(T56=T57,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z56">
-        <f>IF(ISNUMBER(T56),IF(ISNUMBER(T58),IF(T56&gt;T58,1.0,IF(T56=T58,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T56),IF(ISNUMBER(T58),IF(T56&gt;T58,1.0,IF(T56=T58,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA56" s="14">
@@ -7882,27 +7882,27 @@
         <v/>
       </c>
       <c r="U57" s="14">
-        <f>IF(ISNUMBER(S57),IF(ISNUMBER(S55),IF(S57&gt;S55,1.0,IF(S57=S55,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S57),IF(ISNUMBER(S55),IF(S57&gt;S55,1.0,IF(S57=S55,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V57">
-        <f>IF(ISNUMBER(S57),IF(ISNUMBER(S56),IF(S57&gt;S56,1.0,IF(S57=S56,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S57),IF(ISNUMBER(S56),IF(S57&gt;S56,1.0,IF(S57=S56,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W57">
-        <f>IF(ISNUMBER(S57),IF(ISNUMBER(S58),IF(S57&gt;S58,1.0,IF(S57=S58,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S57),IF(ISNUMBER(S58),IF(S57&gt;S58,1.0,IF(S57=S58,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X57">
-        <f>IF(ISNUMBER(T57),IF(ISNUMBER(T55),IF(T57&gt;T55,1.0,IF(T57=T55,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T57),IF(ISNUMBER(T55),IF(T57&gt;T55,1.0,IF(T57=T55,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y57">
-        <f>IF(ISNUMBER(T57),IF(ISNUMBER(T56),IF(T57&gt;T56,1.0,IF(T57=T56,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T57),IF(ISNUMBER(T56),IF(T57&gt;T56,1.0,IF(T57=T56,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z57">
-        <f>IF(ISNUMBER(T57),IF(ISNUMBER(T58),IF(T57&gt;T58,1.0,IF(T57=T58,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T57),IF(ISNUMBER(T58),IF(T57&gt;T58,1.0,IF(T57=T58,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA57" s="14">
@@ -8009,27 +8009,27 @@
         <v/>
       </c>
       <c r="U58" s="21">
-        <f>IF(ISNUMBER(S58),IF(ISNUMBER(S55),IF(S58&gt;S55,1.0,IF(S58=S55,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S58),IF(ISNUMBER(S55),IF(S58&gt;S55,1.0,IF(S58=S55,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="V58" s="15">
-        <f>IF(ISNUMBER(S58),IF(ISNUMBER(S56),IF(S58&gt;S56,1.0,IF(S58=S56,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S58),IF(ISNUMBER(S56),IF(S58&gt;S56,1.0,IF(S58=S56,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="W58" s="15">
-        <f>IF(ISNUMBER(S58),IF(ISNUMBER(S57),IF(S58&gt;S57,1.0,IF(S58=S57,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(S58),IF(ISNUMBER(S57),IF(S58&gt;S57,1.0,IF(S58=S57,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="X58" s="15">
-        <f>IF(ISNUMBER(T58),IF(ISNUMBER(T55),IF(T58&gt;T55,1.0,IF(T58=T55,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T58),IF(ISNUMBER(T55),IF(T58&gt;T55,1.0,IF(T58=T55,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Y58" s="15">
-        <f>IF(ISNUMBER(T58),IF(ISNUMBER(T56),IF(T58&gt;T56,1.0,IF(T58=T56,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T58),IF(ISNUMBER(T56),IF(T58&gt;T56,1.0,IF(T58=T56,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="Z58" s="15">
-        <f>IF(ISNUMBER(T58),IF(ISNUMBER(T57),IF(T58&gt;T57,1.0,IF(T58=T57,0.5,0.0)),""),"")</f>
+        <f>IF(ISNUMBER(T58),IF(ISNUMBER(T57),IF(T58&gt;T57,1.0,IF(T58=T57,0.5,0.0)),0.5),0.5)</f>
         <v/>
       </c>
       <c r="AA58" s="21">

--- a/howell7.xlsx
+++ b/howell7.xlsx
@@ -590,12 +590,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 48</t>
+          <t>Name 46</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name 82</t>
+          <t>Name 39</t>
         </is>
       </c>
       <c r="D10" s="4">
@@ -613,12 +613,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Name 32</t>
+          <t>Name 38</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Name 84</t>
+          <t>Name 35</t>
         </is>
       </c>
       <c r="D11" s="4">
@@ -636,12 +636,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Name 62</t>
+          <t>Name 30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Name 55</t>
+          <t>Name 35</t>
         </is>
       </c>
       <c r="D12" s="4">
@@ -659,12 +659,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Name 82</t>
+          <t>Name 26</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Name 63</t>
+          <t>Name 64</t>
         </is>
       </c>
       <c r="D13" s="4">
@@ -682,12 +682,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Name 79</t>
+          <t>Name 43</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Name 31</t>
+          <t>Name 54</t>
         </is>
       </c>
       <c r="D14" s="4">
@@ -705,12 +705,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Name 46</t>
+          <t>Name 58</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Name 58</t>
+          <t>Name 75</t>
         </is>
       </c>
       <c r="D15" s="4">
@@ -728,12 +728,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Name 29</t>
+          <t>Name 16</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Name 77</t>
+          <t>Name 56</t>
         </is>
       </c>
       <c r="D16" s="4">

--- a/howell7.xlsx
+++ b/howell7.xlsx
@@ -590,12 +590,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 46</t>
+          <t>Name 84</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name 39</t>
+          <t>Name 60</t>
         </is>
       </c>
       <c r="D10" s="4">
@@ -613,12 +613,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Name 38</t>
+          <t>Name 27</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Name 35</t>
+          <t>Name 87</t>
         </is>
       </c>
       <c r="D11" s="4">
@@ -636,12 +636,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Name 30</t>
+          <t>Name 16</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Name 35</t>
+          <t>Name 70</t>
         </is>
       </c>
       <c r="D12" s="4">
@@ -659,12 +659,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Name 26</t>
+          <t>Name 58</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Name 64</t>
+          <t>Name 13</t>
         </is>
       </c>
       <c r="D13" s="4">
@@ -682,12 +682,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Name 43</t>
+          <t>Name 29</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Name 54</t>
+          <t>Name 68</t>
         </is>
       </c>
       <c r="D14" s="4">
@@ -705,12 +705,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Name 58</t>
+          <t>Name 77</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Name 75</t>
+          <t>Name 74</t>
         </is>
       </c>
       <c r="D15" s="4">
@@ -728,12 +728,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Name 16</t>
+          <t>Name 18</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Name 56</t>
+          <t>Name 79</t>
         </is>
       </c>
       <c r="D16" s="4">
